--- a/files/九龙-启德-The Henley II.xlsx
+++ b/files/九龙-启德-The Henley II.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -897,7 +761,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-11-07</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1227,7 +1091,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-22</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1641,7 +1505,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1825,7 +1689,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2055,7 +1919,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2469,7 +2333,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2561,7 +2425,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2883,7 +2747,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2929,7 +2793,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2975,7 +2839,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3297,7 +3161,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3343,7 +3207,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-09</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3389,7 +3253,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3481,7 +3345,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3711,7 +3575,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3757,7 +3621,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3803,7 +3667,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4217,7 +4081,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4309,7 +4173,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4539,7 +4403,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4723,7 +4587,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4815,7 +4679,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4953,7 +4817,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5229,7 +5093,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-16</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5367,7 +5231,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5413,7 +5277,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-20</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5459,7 +5323,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5781,7 +5645,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -6195,7 +6059,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6379,7 +6243,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6609,7 +6473,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6655,7 +6519,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6701,7 +6565,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -7023,7 +6887,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7437,7 +7301,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7621,7 +7485,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7851,7 +7715,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -8131,7 +7995,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8177,7 +8041,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8223,7 +8087,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8269,7 +8133,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-26</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8545,7 +8409,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8591,7 +8455,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8637,7 +8501,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -8683,7 +8547,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -8963,7 +8827,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -9009,7 +8873,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
+          <t>2022-09-05</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9389,7 +9253,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -9435,7 +9299,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-25</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -9527,7 +9391,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -9815,7 +9679,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -9861,7 +9725,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -9953,7 +9817,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-28</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -10237,7 +10101,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -10375,7 +10239,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -10793,7 +10657,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -11077,7 +10941,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-11-06</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -11169,7 +11033,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -11215,7 +11079,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-16</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -11503,7 +11367,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-31</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -11595,7 +11459,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -11641,7 +11505,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -12059,7 +11923,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -12619,7 +12483,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -12899,7 +12763,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -13325,7 +13189,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-19</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -13663,7 +13527,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -13755,7 +13619,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-08</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -14093,7 +13957,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -14185,7 +14049,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -14615,7 +14479,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-16</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -14687,2808 +14551,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Henley II - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>301 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>37 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>261 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1365呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$2,108万
-$36,789/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G6" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$859万
-$22,546/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H6" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$858万
-$22,589/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$3,163万
-$35,618/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,908万
-$34,700/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,908万
-$35,135/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,533万
-$31,998/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,569万
-$27,381/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$835万
-$21,919/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$835万
-$21,962/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$834万
-$22,009/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$919万
-$22,191/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$3,450万
-$38,851/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,886万
-$34,300/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,886万
-$34,736/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,523万
-$31,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>E | 575呎 (2房)
-$1,548万
-$26,915/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$755万
-$19,806/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H8" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$825万
-$21,718/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$825万
-$21,762/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="J8" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$898万
-$21,691/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$3,313万
-$37,309/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,876万
-$34,100/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,873万
-$34,490/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,553万
-$32,412/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>E | 575呎 (2房)
-$1,523万
-$26,483/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$750万
-$19,696/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H9" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$821万
-$21,596/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$820万
-$21,639/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$903万
-$21,808/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$3,081万
-$34,700/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,870万
-$34,000/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,866万
-$34,359/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,506万
-$31,435/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,518万
-$26,499/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$748万
-$19,638/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H10" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$818万
-$21,534/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$818万
-$21,579/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$880万
-$21,260/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$3,072万
-$34,600/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,864万
-$33,900/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,958万
-$36,063/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,580万
-$32,996/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,546万
-$26,980/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$746万
-$19,583/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H11" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$738万
-$19,418/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$745万
-$19,661/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J11" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$878万
-$21,196/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$3,260万
-$36,712/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,859万
-$33,800/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>C | 542呎 (2房)
-$1,855万
-$34,225/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,497万
-$31,255/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,557万
-$27,180/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$744万
-$19,525/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H12" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$736万
-$19,361/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$743万
-$19,606/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J12" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$875万
-$21,135/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$3,215万
-$36,200/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,854万
-$33,700/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,850万
-$34,062/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,493万
-$31,163/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,553万
-$27,101/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$742万
-$19,473/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H13" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$734万
-$19,305/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$898万
-$23,697/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$872万
-$21,074/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$3,189万
-$35,910/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,848万
-$33,600/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,844万
-$33,962/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,488万
-$31,074/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,383万
-$24,133/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G14" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$809万
-$21,246/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H14" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$732万
-$19,252/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I14" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$739万
-$19,492/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J14" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$870万
-$21,013/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$3,179万
-$35,800/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,842万
-$33,500/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,839万
-$33,862/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,547万
-$32,287/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t>E | 575呎 (2房)
-$1,497万
-$26,030/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$807万
-$21,186/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H15" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$884万
-$23,268/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="I15" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$893万
-$23,560/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="J15" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$867万
-$20,949/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$3,030万
-$34,122/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,837万
-$33,400/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,833万
-$33,763/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,480万
-$30,892/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,492万
-$26,045/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$805万
-$21,126/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H16" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$727万
-$19,142/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I16" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$967万
-$25,504/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J16" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$865万
-$20,886/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$3,010万
-$33,896/呎
-(23年-10月)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,832万
-$33,300/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,905万
-$35,080/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-$1,475万
-$30,995/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,519万
-$26,515/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$726万
-$19,050/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H17" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$889万
-$23,399/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="I17" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$964万
-$25,432/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J17" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$862万
-$20,827/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$2,948万
-$33,200/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,820万
-$33,100/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,817万
-$33,463/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,467万
-$30,620/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,557万
-$27,176/呎
-(22年-07月)</t>
-        </is>
-      </c>
-      <c r="G18" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$722万
-$18,938/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H18" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$797万
-$20,982/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$728万
-$19,213/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J18" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$775万
-$18,719/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$3,019万
-$34,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,815万
-$33,000/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,812万
-$33,364/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,462万
-$30,529/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,553万
-$27,096/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$719万
-$18,882/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H19" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$795万
-$20,922/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$880万
-$23,218/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="J19" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$773万
-$18,664/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$2,984万
-$33,600/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,810万
-$32,900/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,806万
-$33,266/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,458万
-$30,440/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>E | 575呎 (2房)
-$1,471万
-$25,578/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$717万
-$18,827/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H20" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$793万
-$20,859/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I20" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$724万
-$19,100/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J20" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$770万
-$18,607/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$3,010万
-$33,900/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,804万
-$32,800/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,801万
-$33,166/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,515万
-$31,626/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,497万
-$26,125/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$715万
-$18,772/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H21" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$790万
-$20,797/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$885万
-$23,346/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="J21" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$768万
-$18,552/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$3,038万
-$34,212/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,798万
-$32,691/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,796万
-$33,066/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,465万
-$30,576/呎
-(23年-12月)</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>E | 575呎 (2房)
-$1,447万
-$25,163/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$713万
-$18,717/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H22" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$788万
-$20,740/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$732万
-$19,312/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J22" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$779万
-$18,814/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$3,110万
-$35,023/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,886万
-$34,300/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 542呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,447万
-$30,210/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>E | 575呎 (2房)
-$1,443万
-$25,088/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$711万
-$18,662/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H23" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$786万
-$20,675/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="I23" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$895万
-$23,604/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="J23" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$763万
-$18,438/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$2,940万
-$33,108/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,741万
-$31,655/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,742万
-$32,081/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,443万
-$30,121/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>E | 575呎 (2房)
-$1,453万
-$25,275/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$933万
-$24,486/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H24" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$932万
-$24,532/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I24" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$951万
-$25,102/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J24" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$842万
-$20,330/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$2,939万
-$33,100/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>C | 542呎 (2房)
-$1,808万
-$33,358/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-$1,438万
-$30,011/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,479万
-$25,819/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$960万
-$25,184/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H25" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$949万
-$24,975/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I25" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$949万
-$25,028/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J25" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$839万
-$20,266/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$2,930万
-$33,000/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 542呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,328万
-$23,176/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G26" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$715万
-$18,764/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H26" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$969万
-$25,490/呎
-(22年-08月)</t>
-        </is>
-      </c>
-      <c r="I26" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$939万
-$24,768/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J26" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$839万
-$20,266/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$2,930万
-$32,995/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 542呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F27" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,505万
-$26,272/呎
-(22年-08月)</t>
-        </is>
-      </c>
-      <c r="G27" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$705万
-$18,497/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H27" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$936万
-$24,644/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I27" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$936万
-$24,692/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J27" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$836万
-$20,205/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$2,920万
-$32,883/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,772万
-$32,640/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F28" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,440万
-$25,136/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G28" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$703万
-$18,441/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H28" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$924万
-$24,315/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I28" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$933万
-$24,605/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J28" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$914万
-$22,080/呎
-(25年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$2,913万
-$32,800/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,766万
-$32,100/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,767万
-$32,540/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,436万
-$25,060/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G29" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$701万
-$18,386/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H29" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$700万
-$18,421/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I29" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$931万
-$24,560/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J29" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$911万
-$22,012/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$2,904万
-$32,700/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>C | 542呎 (2房)
-$1,789万
-$33,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,497万
-$26,134/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G30" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$739万
-$19,392/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H30" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$738万
-$19,429/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I30" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$745万
-$19,661/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J30" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$794万
-$19,167/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$2,859万
-$32,200/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>C | 542呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>E | 575呎 (2房)
-$1,423万
-$24,748/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G31" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$914万
-$23,977/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H31" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$694万
-$18,253/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$922万
-$24,324/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J31" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$745万
-$17,990/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$2,895万
-$32,600/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,678万
-$30,509/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>C | 543呎 (2房)
-$1,729万
-$31,841/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F32" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,463万
-$25,531/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G32" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$911万
-$23,904/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H32" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$692万
-$18,200/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I32" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$919万
-$24,249/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J32" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$900万
-$21,740/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$2,895万
-$32,600/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,754万
-$31,900/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>C | 542呎 (2房)
-$1,756万
-$32,400/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F33" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,463万
-$25,531/呎
-(22年-08月)</t>
-        </is>
-      </c>
-      <c r="G33" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$692万
-$18,164/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H33" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$692万
-$18,200/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I33" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$698万
-$18,426/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J33" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$743万
-$17,935/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C34" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,704万
-$30,982/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>C | 542呎 (2房)
-$1,704万
-$31,439/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F34" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,400万
-$24,433/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G34" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$690万
-$18,108/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H34" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$690万
-$18,145/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I34" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$696万
-$18,370/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J34" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$740万
-$17,880/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-$2,877万
-$32,400/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>C | 542呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F35" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,445万
-$25,218/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G35" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$704万
-$18,487/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H35" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$732万
-$19,263/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I35" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$841万
-$22,198/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="J35" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$895万
-$21,607/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>C | 542呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F36" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,432万
-$24,985/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G36" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$698万
-$18,318/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H36" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$697万
-$18,352/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I36" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$713万
-$18,811/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J36" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$813万
-$19,647/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>C | 542呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F37" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,369万
-$23,899/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G37" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$696万
-$18,260/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H37" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$897万
-$23,613/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I37" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$711万
-$18,754/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J37" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$811万
-$19,586/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>A | 888呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>C | 542呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>D | 476呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F38" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,390万
-$24,250/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G38" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$691万
-$18,148/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H38" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$920万
-$24,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I38" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$706万
-$18,638/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J38" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$806万
-$19,461/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr"/>
-      <c r="C39" s="17" t="inlineStr"/>
-      <c r="D39" s="17" t="inlineStr"/>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>D | 479呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F39" s="19" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,376万
-$24,020/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G39" s="19" t="inlineStr">
-        <is>
-          <t>F | 381呎 (1房)
-$685万
-$17,969/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H39" s="19" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$684万
-$18,002/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I39" s="19" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$702万
-$18,523/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="J39" s="19" t="inlineStr">
-        <is>
-          <t>J | 414呎 (1房)
-$801万
-$19,336/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-启德-The Henley II.xlsx
+++ b/files/九龙-启德-The Henley II.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +142,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +223,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -14551,4 +14730,2808 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1365呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$2108万
+$36,789/呎
+(22年-11月)</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$859万
+$22,546/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$858万
+$22,589/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$3163万
+$35,618/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1908万
+$34,700/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1908万
+$35,135/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1533万
+$31,998/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1569万
+$27,381/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$835万
+$21,919/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$835万
+$21,962/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$834万
+$22,009/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$919万
+$22,191/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$3450万
+$38,851/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1886万
+$34,300/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1886万
+$34,736/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1523万
+$31,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>E | 575呎 (2房)
+$1548万
+$26,915/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$755万
+$19,806/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$825万
+$21,718/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$825万
+$21,762/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$898万
+$21,691/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$3313万
+$37,309/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1876万
+$34,100/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1873万
+$34,490/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1553万
+$32,412/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>E | 575呎 (2房)
+$1523万
+$26,483/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$750万
+$19,696/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$821万
+$21,596/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$820万
+$21,639/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$903万
+$21,808/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$3081万
+$34,700/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1870万
+$34,000/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1866万
+$34,359/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1506万
+$31,435/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1518万
+$26,499/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$748万
+$19,638/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$818万
+$21,534/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$818万
+$21,579/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$880万
+$21,260/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$3072万
+$34,600/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1864万
+$33,900/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1958万
+$36,063/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1580万
+$32,996/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1546万
+$26,980/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$746万
+$19,583/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$738万
+$19,418/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$745万
+$19,661/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$878万
+$21,196/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$3260万
+$36,712/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1859万
+$33,800/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>C | 542呎 (2房)
+$1855万
+$34,225/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1497万
+$31,255/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1557万
+$27,180/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$744万
+$19,525/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$736万
+$19,361/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$743万
+$19,606/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$875万
+$21,135/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$3215万
+$36,200/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1854万
+$33,700/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1850万
+$34,062/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1493万
+$31,163/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1553万
+$27,101/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$742万
+$19,473/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$734万
+$19,305/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$898万
+$23,697/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$872万
+$21,074/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$3189万
+$35,910/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1848万
+$33,600/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1844万
+$33,962/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1488万
+$31,074/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1383万
+$24,133/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$809万
+$21,246/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$732万
+$19,252/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$739万
+$19,492/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$870万
+$21,013/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$3179万
+$35,800/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1842万
+$33,500/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1839万
+$33,862/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1547万
+$32,287/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>E | 575呎 (2房)
+$1497万
+$26,030/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$807万
+$21,186/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$884万
+$23,268/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$893万
+$23,560/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$867万
+$20,949/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$3030万
+$34,122/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1837万
+$33,400/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1833万
+$33,763/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1480万
+$30,892/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1492万
+$26,045/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$805万
+$21,126/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$727万
+$19,142/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$967万
+$25,504/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$865万
+$20,886/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$3010万
+$33,896/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1832万
+$33,300/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1905万
+$35,080/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$1475万
+$30,995/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1519万
+$26,515/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$726万
+$19,050/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$889万
+$23,399/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$964万
+$25,432/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$862万
+$20,827/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$2948万
+$33,200/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1820万
+$33,100/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1817万
+$33,463/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1467万
+$30,620/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1557万
+$27,176/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$722万
+$18,938/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$797万
+$20,982/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$728万
+$19,213/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$775万
+$18,719/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$3019万
+$34,000/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1815万
+$33,000/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1812万
+$33,364/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1462万
+$30,529/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1553万
+$27,096/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$719万
+$18,882/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$795万
+$20,922/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$880万
+$23,218/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$773万
+$18,664/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$2984万
+$33,600/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1810万
+$32,900/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1806万
+$33,266/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1458万
+$30,440/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>E | 575呎 (2房)
+$1471万
+$25,578/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$717万
+$18,827/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$793万
+$20,859/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$724万
+$19,100/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$770万
+$18,607/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$3010万
+$33,900/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1804万
+$32,800/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1801万
+$33,166/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1515万
+$31,626/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1497万
+$26,125/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$715万
+$18,772/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$790万
+$20,797/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$885万
+$23,346/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$768万
+$18,552/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$3038万
+$34,212/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1798万
+$32,691/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1796万
+$33,066/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1465万
+$30,576/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>E | 575呎 (2房)
+$1447万
+$25,163/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$713万
+$18,717/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$788万
+$20,740/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$732万
+$19,312/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$779万
+$18,814/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$3110万
+$35,023/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1886万
+$34,300/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 542呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1447万
+$30,210/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>E | 575呎 (2房)
+$1443万
+$25,088/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$711万
+$18,662/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$786万
+$20,675/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$895万
+$23,604/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$763万
+$18,438/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$2940万
+$33,108/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1741万
+$31,655/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1742万
+$32,081/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1443万
+$30,121/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>E | 575呎 (2房)
+$1453万
+$25,275/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$933万
+$24,486/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$932万
+$24,532/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$951万
+$25,102/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="J23" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$842万
+$20,330/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$2939万
+$33,100/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>C | 542呎 (2房)
+$1808万
+$33,358/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+$1438万
+$30,011/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1479万
+$25,819/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$960万
+$25,184/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$949万
+$24,975/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$949万
+$25,028/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$839万
+$20,266/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$2930万
+$33,000/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 542呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1328万
+$23,176/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$715万
+$18,764/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$969万
+$25,490/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$939万
+$24,768/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$839万
+$20,266/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$2930万
+$32,995/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 542呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1505万
+$26,272/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$705万
+$18,497/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$936万
+$24,644/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$936万
+$24,692/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$836万
+$20,205/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$2920万
+$32,883/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1772万
+$32,640/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1440万
+$25,136/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$703万
+$18,441/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$924万
+$24,315/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$933万
+$24,605/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$914万
+$22,080/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$2913万
+$32,800/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1766万
+$32,100/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1767万
+$32,540/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1436万
+$25,060/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$701万
+$18,386/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$700万
+$18,421/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I28" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$931万
+$24,560/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$911万
+$22,012/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$2904万
+$32,700/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>C | 542呎 (2房)
+$1789万
+$33,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1497万
+$26,134/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$739万
+$19,392/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$738万
+$19,429/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$745万
+$19,661/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$794万
+$19,167/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$2859万
+$32,200/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 542呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>E | 575呎 (2房)
+$1423万
+$24,748/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$914万
+$23,977/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$694万
+$18,253/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I30" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$922万
+$24,324/呎
+(22年-11月)</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$745万
+$17,990/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$2895万
+$32,600/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1678万
+$30,509/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1729万
+$31,841/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1463万
+$25,531/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$911万
+$23,904/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$692万
+$18,200/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I31" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$919万
+$24,249/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$900万
+$21,740/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$2895万
+$32,600/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1754万
+$31,900/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>C | 542呎 (2房)
+$1756万
+$32,400/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1463万
+$25,531/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$692万
+$18,164/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$692万
+$18,200/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I32" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$698万
+$18,426/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$743万
+$17,935/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1704万
+$30,982/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>C | 542呎 (2房)
+$1704万
+$31,439/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1400万
+$24,433/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$690万
+$18,108/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$690万
+$18,145/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I33" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$696万
+$18,370/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$740万
+$17,880/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+$2877万
+$32,400/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 542呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1445万
+$25,218/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$704万
+$18,487/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$732万
+$19,263/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I34" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$841万
+$22,198/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$895万
+$21,607/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 542呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1432万
+$24,985/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$698万
+$18,318/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$697万
+$18,352/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I35" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$713万
+$18,811/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$813万
+$19,647/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>C | 542呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1369万
+$23,899/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$696万
+$18,260/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$897万
+$23,613/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="I36" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$711万
+$18,754/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J36" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$811万
+$19,586/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>A | 888呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>C | 542呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1390万
+$24,250/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$691万
+$18,148/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H37" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$920万
+$24,200/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="I37" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$706万
+$18,638/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J37" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$806万
+$19,461/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr"/>
+      <c r="C38" s="21" t="inlineStr"/>
+      <c r="D38" s="21" t="inlineStr"/>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>D | 479呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1376万
+$24,020/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>F | 381呎 (1房)
+$685万
+$17,969/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H38" s="23" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$684万
+$18,002/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I38" s="23" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$702万
+$18,523/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>J | 414呎 (1房)
+$801万
+$19,336/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-The Henley II.xlsx
+++ b/files/九龙-启德-The Henley II.xlsx
@@ -653,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="E223" s="4" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
@@ -10932,14 +10932,14 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
         <v>17886000</v>
       </c>
       <c r="I223" s="5" t="n">
-        <v>33000</v>
+        <v>32939</v>
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
@@ -16782,10 +16782,10 @@
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>C | 542呎 (2房)
+          <t>C | 543呎 (2房)
 $1789万
-$33,000/呎
-(26年-06月)</t>
+$32,939/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">

--- a/files/九龙-启德-The Henley II.xlsx
+++ b/files/九龙-启德-The Henley II.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J303"/>
+  <dimension ref="A1:N303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -713,6 +717,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -763,6 +787,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -813,6 +857,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -859,6 +923,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>8583900</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>22589</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -905,6 +985,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>8590200</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>22546</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -951,6 +1047,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>21080000</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>36789</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1001,6 +1113,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1051,6 +1183,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1097,6 +1249,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>9187100</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>22191</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1143,6 +1311,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>8341300</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>22009</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1189,6 +1373,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>8345700</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>21962</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1235,6 +1435,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>8351000</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>21919</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1281,6 +1497,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>15689200</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>27381</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1327,6 +1559,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>15327200</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>31998</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1373,6 +1621,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>19078400</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>35135</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1419,6 +1683,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>19085000</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>34700</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1465,6 +1745,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>31628800</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>35618</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1511,6 +1807,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>8980000</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>21691</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1557,6 +1869,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>8247700</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>21762</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1603,6 +1931,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>8253000</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>21718</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1649,6 +1993,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>7546000</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>19806</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1695,6 +2055,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>15476100</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>26915</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1741,6 +2117,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>15232000</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>31800</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1787,6 +2179,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>18861600</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>34736</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1833,6 +2241,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>18865000</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>34300</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1879,6 +2303,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>38851</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1925,6 +2365,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>9028700</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>21808</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1971,6 +2427,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>8201300</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>21639</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2017,6 +2489,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>8206600</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>21596</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2063,6 +2551,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>7504000</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>19696</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2109,6 +2613,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>15227500</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>26483</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2155,6 +2675,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>15525220</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>32412</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2201,6 +2737,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>18728000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>34490</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2247,6 +2799,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>18755000</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>34100</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2293,6 +2861,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>33130000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>37309</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2339,6 +2923,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>8801600</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>21260</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2385,6 +2985,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>8178600</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>21579</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2431,6 +3047,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>8183000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>21534</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2477,6 +3109,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>7482100</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>19638</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2523,6 +3171,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>15183800</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>26499</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2569,6 +3233,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>15057500</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>31435</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2615,6 +3295,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>18657000</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>34359</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2661,6 +3357,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>18700000</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>34000</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2707,6 +3419,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>30813600</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>34700</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2753,6 +3481,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>8775300</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>21196</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2799,6 +3543,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>7451500</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>19661</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2845,6 +3605,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>7378800</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>19418</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2891,6 +3667,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>7461100</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>19583</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2937,6 +3729,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>15459800</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>26980</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2983,6 +3791,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>15805000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>32996</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3029,6 +3853,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>19582000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>36063</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3075,6 +3915,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>18645000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3121,6 +3977,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>30724800</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>34600</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3167,6 +4039,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>8750000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>21135</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3213,6 +4101,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>7430500</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>19606</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3259,6 +4163,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>7357000</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>19361</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3305,6 +4225,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>7439200</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>19525</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3351,6 +4287,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>15574100</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>27180</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3397,6 +4349,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>14971000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>31255</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3443,6 +4411,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>18549700</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>34225</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3489,6 +4473,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>18590000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>33800</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3535,6 +4535,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>32600700</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>36712</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3581,6 +4597,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>8724600</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>21074</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3627,6 +4659,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>8981000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>23697</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3673,6 +4721,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>7336000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>19305</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3719,6 +4783,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>7419100</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>19473</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3765,6 +4845,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>15529000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>27101</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3811,6 +4907,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>14927300</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>31163</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3857,6 +4969,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>18495500</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>34062</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3903,6 +5031,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>18535000</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>33700</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3949,6 +5093,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>32145600</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>36200</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3995,6 +5155,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>8699200</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>21013</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4041,6 +5217,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>7387600</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>19492</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4087,6 +5279,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>7315800</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>19252</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4133,6 +5341,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>8094600</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>21246</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4179,6 +5403,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>13828000</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>24133</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4225,6 +5465,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>14884600</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>31074</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4271,6 +5527,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>18441400</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>33962</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4317,6 +5589,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>18480000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>33600</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4363,6 +5651,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>31888000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>35910</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4409,6 +5713,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>8673000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>20949</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4455,6 +5775,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>8929300</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>23560</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4501,6 +5837,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>8841800</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>23268</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4547,6 +5899,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>8071800</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>21186</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4593,6 +5961,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>14967200</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>26030</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4639,6 +6023,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>15465700</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>32287</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4685,6 +6085,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>18387200</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>33862</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4731,6 +6147,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>18425000</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>33500</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4777,6 +6209,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>31790400</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>35800</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4823,6 +6271,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>8646700</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>20886</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4869,6 +6333,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>9666200</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>25504</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4915,6 +6395,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>7273800</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>19142</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4961,6 +6457,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>8049100</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>21126</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5007,6 +6519,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>14923500</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>26045</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5053,6 +6581,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>14797200</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>30892</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5099,6 +6643,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>18333100</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>33763</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5145,6 +6705,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>18370000</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>33400</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5191,6 +6767,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>30300000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>34122</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5237,6 +6829,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>8622200</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>20827</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5283,6 +6891,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>9638700</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>25432</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5329,6 +6953,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>8891500</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>23399</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5375,6 +7015,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>7258100</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>19050</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5421,6 +7077,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>15193100</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>26515</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5467,6 +7139,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>14753500</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>30995</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5513,6 +7201,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>19048500</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>35080</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5559,6 +7263,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>18315000</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>33300</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5605,6 +7325,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>30100000</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>33896</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5651,6 +7387,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>7749800</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>18719</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5697,6 +7449,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>7281700</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>19213</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5743,6 +7511,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>7973000</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>20982</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5789,6 +7573,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>7215200</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>18938</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5835,6 +7635,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>15572000</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>27176</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5881,6 +7697,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>14667000</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>30620</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5927,6 +7759,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>18170600</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>33463</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5973,6 +7821,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>18205000</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>33100</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6019,6 +7883,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>29481600</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>33200</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6065,6 +7945,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>7727100</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>18664</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6111,6 +8007,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>8799800</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>23218</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6157,6 +8069,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>7950200</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>20922</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6203,6 +8131,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>7194200</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>18882</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6249,6 +8193,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>15526000</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>27096</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6295,6 +8255,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>14623300</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>30529</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6341,6 +8317,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>18116500</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>33364</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6387,6 +8379,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>18150000</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>33000</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6433,6 +8441,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>30192000</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>34000</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6479,6 +8503,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>7703500</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>18607</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6525,6 +8565,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>7238800</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>19100</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6571,6 +8627,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>7926600</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>20859</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6617,6 +8689,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>7173200</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>18827</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6663,6 +8751,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>14707200</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>25578</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6709,6 +8813,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>14580600</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>30440</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6755,6 +8875,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>18063300</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>33266</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6801,6 +8937,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>18095000</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>32900</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6847,6 +8999,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>29836800</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>33600</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6893,6 +9061,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>7680700</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>18552</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6939,6 +9123,22 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>8848200</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>23346</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6985,6 +9185,22 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>7903000</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>20797</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7031,6 +9247,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>7152200</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>18772</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7077,6 +9309,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>14969500</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>26125</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7123,6 +9371,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>15148900</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>31626</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7169,6 +9433,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>18009100</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>33166</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7215,6 +9495,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>18040000</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>32800</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7261,6 +9557,22 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>30103200</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7307,6 +9619,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>7789200</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>18814</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7353,6 +9681,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>7319300</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>19312</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7399,6 +9743,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>7881100</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>20740</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7445,6 +9805,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>7131200</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>18717</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7491,6 +9867,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>14468500</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>25163</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7537,6 +9929,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>14645700</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>30576</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7583,6 +9991,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>17955000</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>33066</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7629,6 +10053,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>17980000</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>32691</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7675,6 +10115,22 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>30380000</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>34212</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7721,6 +10177,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>7633500</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>18438</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7767,6 +10239,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>8946000</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>23604</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7813,6 +10301,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>7856600</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>20675</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7859,6 +10363,22 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>7110200</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>18662</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7905,6 +10425,22 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>14425700</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>25088</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7951,6 +10487,22 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>14470400</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>30210</v>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8001,6 +10553,26 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -8047,6 +10619,22 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>18865000</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>34300</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8093,6 +10681,22 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>31100000</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>35023</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8139,6 +10743,22 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>8416600</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>20330</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8185,6 +10805,22 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>9513600</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>25102</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8231,6 +10867,22 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>9322300</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>24532</v>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8277,6 +10929,22 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>9329000</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>24486</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8323,6 +10991,22 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>14533400</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>25275</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8369,6 +11053,22 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>14428000</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>30121</v>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8415,6 +11115,22 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>17420000</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>32081</v>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8461,6 +11177,22 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="5" t="n">
+        <v>17410000</v>
+      </c>
+      <c r="L170" s="5" t="n">
+        <v>31655</v>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8507,6 +11239,22 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>29400000</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>33108</v>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8553,6 +11301,22 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>8390300</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>20266</v>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8599,6 +11363,22 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>9485700</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>25028</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8645,6 +11425,22 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>9490400</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>24975</v>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8691,6 +11487,22 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>9595100</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>25184</v>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8737,6 +11549,22 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>14794400</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>25819</v>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8783,6 +11611,22 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>14375200</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>30011</v>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8829,6 +11673,22 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>18080000</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>33358</v>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8879,6 +11739,26 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -8925,6 +11805,22 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>29393000</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>33100</v>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8971,6 +11867,22 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>8390300</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>20266</v>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9017,6 +11929,22 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>9386900</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>24768</v>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9063,6 +11991,22 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>9686100</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>25490</v>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9109,6 +12053,22 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>7149000</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>18764</v>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9155,6 +12115,22 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>13280000</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>23176</v>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9205,6 +12181,26 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -9255,6 +12251,26 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L187" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -9305,6 +12321,26 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -9351,6 +12387,22 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>29304000</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>33000</v>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9397,6 +12449,22 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>8365000</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>20205</v>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9443,6 +12511,22 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="5" t="n">
+        <v>9358400</v>
+      </c>
+      <c r="L191" s="5" t="n">
+        <v>24692</v>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9489,6 +12573,22 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>9364800</v>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>24644</v>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9535,6 +12635,22 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>7047200</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>18497</v>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9581,6 +12697,22 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>15053900</v>
+      </c>
+      <c r="L194" s="5" t="n">
+        <v>26272</v>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9631,6 +12763,26 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L195" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -9681,6 +12833,26 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L196" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -9731,6 +12903,26 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L197" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -9777,6 +12969,22 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>29300000</v>
+      </c>
+      <c r="L198" s="5" t="n">
+        <v>32995</v>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9823,6 +13031,22 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>9141100</v>
+      </c>
+      <c r="L199" s="5" t="n">
+        <v>22080</v>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9869,6 +13093,22 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" s="5" t="n">
+        <v>9325200</v>
+      </c>
+      <c r="L200" s="5" t="n">
+        <v>24605</v>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9915,6 +13155,22 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>9239700</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>24315</v>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9961,6 +13217,22 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>7026200</v>
+      </c>
+      <c r="L202" s="5" t="n">
+        <v>18441</v>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10007,6 +13279,22 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="n">
+        <v>14402900</v>
+      </c>
+      <c r="L203" s="5" t="n">
+        <v>25136</v>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10057,6 +13345,26 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L204" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -10103,6 +13411,22 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>17723400</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>32640</v>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10153,6 +13477,26 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -10199,6 +13543,22 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>29200000</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>32883</v>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10245,6 +13605,22 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="n">
+        <v>9113100</v>
+      </c>
+      <c r="L208" s="5" t="n">
+        <v>22012</v>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10291,6 +13667,22 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="n">
+        <v>9308100</v>
+      </c>
+      <c r="L209" s="5" t="n">
+        <v>24560</v>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10337,6 +13729,22 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" s="5" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="L210" s="5" t="n">
+        <v>18421</v>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10383,6 +13791,22 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>7005200</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>18386</v>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10429,6 +13853,22 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>14359200</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>25060</v>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10479,6 +13919,26 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -10525,6 +13985,22 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="n">
+        <v>17669200</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>32540</v>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10571,6 +14047,22 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>17655000</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>32100</v>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10617,6 +14109,22 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" s="5" t="n">
+        <v>29126400</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>32800</v>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10663,6 +14171,22 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="5" t="n">
+        <v>7935300</v>
+      </c>
+      <c r="L217" s="5" t="n">
+        <v>19167</v>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10709,6 +14233,22 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>7451500</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>19661</v>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10755,6 +14295,22 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" s="5" t="n">
+        <v>7383200</v>
+      </c>
+      <c r="L219" s="5" t="n">
+        <v>19429</v>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10801,6 +14357,22 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" s="5" t="n">
+        <v>7388500</v>
+      </c>
+      <c r="L220" s="5" t="n">
+        <v>19392</v>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10847,6 +14419,22 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>14974800</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>26134</v>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10897,6 +14485,26 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -10943,6 +14551,22 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>17886000</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>32939</v>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10993,6 +14617,26 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -11039,6 +14683,22 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>29037600</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>32700</v>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11085,6 +14745,22 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" s="5" t="n">
+        <v>7448000</v>
+      </c>
+      <c r="L226" s="5" t="n">
+        <v>17990</v>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11131,6 +14807,22 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>9218800</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>24324</v>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11177,6 +14869,22 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>6936100</v>
+      </c>
+      <c r="L228" s="5" t="n">
+        <v>18253</v>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11223,6 +14931,22 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" s="5" t="n">
+        <v>9135200</v>
+      </c>
+      <c r="L229" s="5" t="n">
+        <v>23977</v>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11269,6 +14993,22 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>14230000</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>24748</v>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11319,6 +15059,26 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -11369,6 +15129,26 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -11419,6 +15199,26 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -11465,6 +15265,22 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>28593600</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>32200</v>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11511,6 +15327,22 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>9000200</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>21740</v>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11557,6 +15389,22 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" s="5" t="n">
+        <v>9190300</v>
+      </c>
+      <c r="L236" s="5" t="n">
+        <v>24249</v>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11603,6 +15451,22 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>6916000</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>18200</v>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11649,6 +15513,22 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" s="5" t="n">
+        <v>9107600</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>23904</v>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11695,6 +15575,22 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>14629200</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>25531</v>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11745,6 +15641,26 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -11791,6 +15707,22 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" s="5" t="n">
+        <v>17289800</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>31841</v>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11837,6 +15769,22 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>16780000</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>30509</v>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11872,7 +15820,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -11883,6 +15831,22 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" s="5" t="n">
+        <v>28948800</v>
+      </c>
+      <c r="L243" s="5" t="n">
+        <v>32600</v>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11929,6 +15893,22 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" s="5" t="n">
+        <v>7425200</v>
+      </c>
+      <c r="L244" s="5" t="n">
+        <v>17935</v>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11975,6 +15955,22 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" s="5" t="n">
+        <v>6983300</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>18426</v>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12021,6 +16017,22 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" s="5" t="n">
+        <v>6916000</v>
+      </c>
+      <c r="L246" s="5" t="n">
+        <v>18200</v>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12067,6 +16079,22 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" s="5" t="n">
+        <v>6920300</v>
+      </c>
+      <c r="L247" s="5" t="n">
+        <v>18164</v>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12113,6 +16141,22 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="n">
+        <v>14629200</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>25531</v>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12163,6 +16207,26 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -12209,6 +16273,22 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="n">
+        <v>17560800</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>32400</v>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12255,6 +16335,22 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" s="5" t="n">
+        <v>17545000</v>
+      </c>
+      <c r="L251" s="5" t="n">
+        <v>31900</v>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12290,7 +16386,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -12301,6 +16397,22 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" s="5" t="n">
+        <v>28948800</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>32600</v>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12347,6 +16459,22 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" s="5" t="n">
+        <v>7402500</v>
+      </c>
+      <c r="L253" s="5" t="n">
+        <v>17880</v>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12393,6 +16521,22 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" s="5" t="n">
+        <v>6962300</v>
+      </c>
+      <c r="L254" s="5" t="n">
+        <v>18370</v>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12439,6 +16583,22 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" s="5" t="n">
+        <v>6895000</v>
+      </c>
+      <c r="L255" s="5" t="n">
+        <v>18145</v>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12485,6 +16645,22 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>6899300</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>18108</v>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12531,6 +16707,22 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" s="5" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>24433</v>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12581,6 +16773,26 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -12627,6 +16839,22 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" s="5" t="n">
+        <v>17040000</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>31439</v>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12673,6 +16901,22 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" s="5" t="n">
+        <v>17040000</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>30982</v>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12723,6 +16967,26 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -12769,6 +17033,22 @@
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" s="5" t="n">
+        <v>8945100</v>
+      </c>
+      <c r="L262" s="5" t="n">
+        <v>21607</v>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12815,6 +17095,22 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>8413100</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>22198</v>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12861,6 +17157,22 @@
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>7320000</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>19263</v>
+      </c>
+      <c r="M264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12907,6 +17219,22 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>7043700</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>18487</v>
+      </c>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12953,6 +17281,22 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" s="5" t="n">
+        <v>14450000</v>
+      </c>
+      <c r="L266" s="5" t="n">
+        <v>25218</v>
+      </c>
+      <c r="M266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13003,6 +17347,26 @@
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L267" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M267" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -13053,6 +17417,26 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -13103,6 +17487,26 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K269" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L269" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M269" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N269" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -13149,6 +17553,22 @@
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K270" s="5" t="n">
+        <v>28771200</v>
+      </c>
+      <c r="L270" s="5" t="n">
+        <v>32400</v>
+      </c>
+      <c r="M270" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N270" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13195,6 +17615,22 @@
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" s="5" t="n">
+        <v>8134000</v>
+      </c>
+      <c r="L271" s="5" t="n">
+        <v>19647</v>
+      </c>
+      <c r="M271" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N271" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13241,6 +17677,22 @@
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" s="5" t="n">
+        <v>7129500</v>
+      </c>
+      <c r="L272" s="5" t="n">
+        <v>18811</v>
+      </c>
+      <c r="M272" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13287,6 +17739,22 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K273" s="5" t="n">
+        <v>6973700</v>
+      </c>
+      <c r="L273" s="5" t="n">
+        <v>18352</v>
+      </c>
+      <c r="M273" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N273" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13333,6 +17801,22 @@
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K274" s="5" t="n">
+        <v>6979000</v>
+      </c>
+      <c r="L274" s="5" t="n">
+        <v>18318</v>
+      </c>
+      <c r="M274" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N274" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13379,6 +17863,22 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K275" s="5" t="n">
+        <v>14316300</v>
+      </c>
+      <c r="L275" s="5" t="n">
+        <v>24985</v>
+      </c>
+      <c r="M275" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N275" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13429,6 +17929,26 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K276" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L276" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M276" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N276" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -13479,6 +17999,26 @@
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K277" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L277" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M277" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N277" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -13529,6 +18069,26 @@
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K278" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L278" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M278" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N278" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -13579,6 +18139,26 @@
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K279" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L279" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M279" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N279" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -13625,6 +18205,22 @@
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K280" s="5" t="n">
+        <v>8108600</v>
+      </c>
+      <c r="L280" s="5" t="n">
+        <v>19586</v>
+      </c>
+      <c r="M280" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N280" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13671,6 +18267,22 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K281" s="5" t="n">
+        <v>7107600</v>
+      </c>
+      <c r="L281" s="5" t="n">
+        <v>18754</v>
+      </c>
+      <c r="M281" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N281" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13717,6 +18329,22 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" s="5" t="n">
+        <v>8973100</v>
+      </c>
+      <c r="L282" s="5" t="n">
+        <v>23613</v>
+      </c>
+      <c r="M282" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13763,6 +18391,22 @@
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K283" s="5" t="n">
+        <v>6957100</v>
+      </c>
+      <c r="L283" s="5" t="n">
+        <v>18260</v>
+      </c>
+      <c r="M283" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N283" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13809,6 +18453,22 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K284" s="5" t="n">
+        <v>13694200</v>
+      </c>
+      <c r="L284" s="5" t="n">
+        <v>23899</v>
+      </c>
+      <c r="M284" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N284" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13859,6 +18519,26 @@
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K285" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L285" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M285" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N285" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -13909,6 +18589,26 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K286" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L286" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M286" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N286" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -13959,6 +18659,26 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K287" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L287" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M287" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N287" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -14009,6 +18729,26 @@
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K288" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L288" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M288" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N288" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -14055,6 +18795,22 @@
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K289" s="5" t="n">
+        <v>8057000</v>
+      </c>
+      <c r="L289" s="5" t="n">
+        <v>19461</v>
+      </c>
+      <c r="M289" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N289" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14101,6 +18857,22 @@
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K290" s="5" t="n">
+        <v>7063800</v>
+      </c>
+      <c r="L290" s="5" t="n">
+        <v>18638</v>
+      </c>
+      <c r="M290" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N290" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14147,6 +18919,22 @@
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K291" s="5" t="n">
+        <v>9196100</v>
+      </c>
+      <c r="L291" s="5" t="n">
+        <v>24200</v>
+      </c>
+      <c r="M291" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N291" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14193,6 +18981,22 @@
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K292" s="5" t="n">
+        <v>6914200</v>
+      </c>
+      <c r="L292" s="5" t="n">
+        <v>18148</v>
+      </c>
+      <c r="M292" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N292" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14239,6 +19043,22 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K293" s="5" t="n">
+        <v>13895200</v>
+      </c>
+      <c r="L293" s="5" t="n">
+        <v>24250</v>
+      </c>
+      <c r="M293" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N293" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14289,6 +19109,26 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K294" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L294" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M294" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N294" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -14339,6 +19179,26 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K295" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L295" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M295" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N295" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -14389,6 +19249,26 @@
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K296" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L296" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M296" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N296" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -14439,6 +19319,26 @@
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K297" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L297" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M297" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N297" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -14485,6 +19385,22 @@
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K298" s="5" t="n">
+        <v>8005300</v>
+      </c>
+      <c r="L298" s="5" t="n">
+        <v>19336</v>
+      </c>
+      <c r="M298" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N298" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14531,6 +19447,22 @@
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K299" s="5" t="n">
+        <v>7020100</v>
+      </c>
+      <c r="L299" s="5" t="n">
+        <v>18523</v>
+      </c>
+      <c r="M299" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N299" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14577,6 +19509,22 @@
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K300" s="5" t="n">
+        <v>6840700</v>
+      </c>
+      <c r="L300" s="5" t="n">
+        <v>18002</v>
+      </c>
+      <c r="M300" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N300" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14623,6 +19571,22 @@
       </c>
       <c r="J301" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K301" s="5" t="n">
+        <v>6846000</v>
+      </c>
+      <c r="L301" s="5" t="n">
+        <v>17969</v>
+      </c>
+      <c r="M301" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N301" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14669,6 +19633,22 @@
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K302" s="5" t="n">
+        <v>13763300</v>
+      </c>
+      <c r="L302" s="5" t="n">
+        <v>24020</v>
+      </c>
+      <c r="M302" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N302" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14719,13 +19699,33 @@
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K303" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L303" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M303" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N303" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -14905,7 +19905,7 @@
           <t>E | 573呎 (2房)
 $2108万
 $36,789/呎
-(22年-11月)</t>
+(22年-11月-07日)</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
@@ -14913,7 +19913,7 @@
           <t>F | 381呎 (1房)
 $859万
 $22,546/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
@@ -14921,7 +19921,7 @@
           <t>G | 380呎 (1房)
 $858万
 $22,589/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -14952,7 +19952,7 @@
           <t>A | 888呎 (3房)
 $3163万
 $35,618/呎
-(25年-04月)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -14960,7 +19960,7 @@
           <t>B | 550呎 (2房)
 $1908万
 $34,700/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -14968,7 +19968,7 @@
           <t>C | 543呎 (2房)
 $1908万
 $35,135/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -14976,7 +19976,7 @@
           <t>D | 479呎 (2房)
 $1533万
 $31,998/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -14984,7 +19984,7 @@
           <t>E | 573呎 (2房)
 $1569万
 $27,381/呎
-(23年-06月)</t>
+(23年-06月-22日)</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
@@ -14992,7 +19992,7 @@
           <t>F | 381呎 (1房)
 $835万
 $21,919/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -15000,7 +20000,7 @@
           <t>G | 380呎 (1房)
 $835万
 $21,962/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
@@ -15008,7 +20008,7 @@
           <t>H | 379呎 (1房)
 $834万
 $22,009/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
@@ -15016,7 +20016,7 @@
           <t>J | 414呎 (1房)
 $919万
 $22,191/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
     </row>
@@ -15031,7 +20031,7 @@
           <t>A | 888呎 (3房)
 $3450万
 $38,851/呎
-(22年-05月)</t>
+(22年-05月-23日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -15039,7 +20039,7 @@
           <t>B | 550呎 (2房)
 $1886万
 $34,300/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -15047,7 +20047,7 @@
           <t>C | 543呎 (2房)
 $1886万
 $34,736/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -15055,7 +20055,7 @@
           <t>D | 479呎 (2房)
 $1523万
 $31,800/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -15063,7 +20063,7 @@
           <t>E | 575呎 (2房)
 $1548万
 $26,915/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -15071,7 +20071,7 @@
           <t>F | 381呎 (1房)
 $755万
 $19,806/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
@@ -15079,7 +20079,7 @@
           <t>G | 380呎 (1房)
 $825万
 $21,718/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
@@ -15087,7 +20087,7 @@
           <t>H | 379呎 (1房)
 $825万
 $21,762/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
@@ -15095,7 +20095,7 @@
           <t>J | 414呎 (1房)
 $898万
 $21,691/呎
-(25年-08月)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -15110,7 +20110,7 @@
           <t>A | 888呎 (3房)
 $3313万
 $37,309/呎
-(23年-11月)</t>
+(23年-11月-30日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -15118,7 +20118,7 @@
           <t>B | 550呎 (2房)
 $1876万
 $34,100/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -15126,7 +20126,7 @@
           <t>C | 543呎 (2房)
 $1873万
 $34,490/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -15134,7 +20134,7 @@
           <t>D | 479呎 (2房)
 $1553万
 $32,412/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -15142,7 +20142,7 @@
           <t>E | 575呎 (2房)
 $1523万
 $26,483/呎
-(22年-07月)</t>
+(22年-07月-21日)</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -15150,7 +20150,7 @@
           <t>F | 381呎 (1房)
 $750万
 $19,696/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -15158,7 +20158,7 @@
           <t>G | 380呎 (1房)
 $821万
 $21,596/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
@@ -15166,7 +20166,7 @@
           <t>H | 379呎 (1房)
 $820万
 $21,639/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
@@ -15174,7 +20174,7 @@
           <t>J | 414呎 (1房)
 $903万
 $21,808/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
     </row>
@@ -15189,7 +20189,7 @@
           <t>A | 888呎 (3房)
 $3081万
 $34,700/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -15197,7 +20197,7 @@
           <t>B | 550呎 (2房)
 $1870万
 $34,000/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -15205,7 +20205,7 @@
           <t>C | 543呎 (2房)
 $1866万
 $34,359/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -15213,7 +20213,7 @@
           <t>D | 479呎 (2房)
 $1506万
 $31,435/呎
-(25年-02月)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -15221,7 +20221,7 @@
           <t>E | 573呎 (2房)
 $1518万
 $26,499/呎
-(22年-07月)</t>
+(22年-07月-24日)</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
@@ -15229,7 +20229,7 @@
           <t>F | 381呎 (1房)
 $748万
 $19,638/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
@@ -15237,7 +20237,7 @@
           <t>G | 380呎 (1房)
 $818万
 $21,534/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -15245,7 +20245,7 @@
           <t>H | 379呎 (1房)
 $818万
 $21,579/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr">
@@ -15253,7 +20253,7 @@
           <t>J | 414呎 (1房)
 $880万
 $21,260/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -15268,7 +20268,7 @@
           <t>A | 888呎 (3房)
 $3072万
 $34,600/呎
-(25年-03月)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -15276,7 +20276,7 @@
           <t>B | 550呎 (2房)
 $1864万
 $33,900/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -15284,7 +20284,7 @@
           <t>C | 543呎 (2房)
 $1958万
 $36,063/呎
-(22年-10月)</t>
+(22年-10月-26日)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -15292,7 +20292,7 @@
           <t>D | 479呎 (2房)
 $1580万
 $32,996/呎
-(22年-09月)</t>
+(22年-09月-04日)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -15300,7 +20300,7 @@
           <t>E | 573呎 (2房)
 $1546万
 $26,980/呎
-(22年-07月)</t>
+(22年-07月-27日)</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
@@ -15308,7 +20308,7 @@
           <t>F | 381呎 (1房)
 $746万
 $19,583/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -15316,7 +20316,7 @@
           <t>G | 380呎 (1房)
 $738万
 $19,418/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
@@ -15324,7 +20324,7 @@
           <t>H | 379呎 (1房)
 $745万
 $19,661/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
@@ -15332,7 +20332,7 @@
           <t>J | 414呎 (1房)
 $878万
 $21,196/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -15347,7 +20347,7 @@
           <t>A | 888呎 (3房)
 $3260万
 $36,712/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -15355,7 +20355,7 @@
           <t>B | 550呎 (2房)
 $1859万
 $33,800/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -15363,7 +20363,7 @@
           <t>C | 542呎 (2房)
 $1855万
 $34,225/呎
-(22年-12月)</t>
+(22年-12月-18日)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -15371,7 +20371,7 @@
           <t>D | 479呎 (2房)
 $1497万
 $31,255/呎
-(23年-01月)</t>
+(23年-01月-09日)</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
@@ -15379,7 +20379,7 @@
           <t>E | 573呎 (2房)
 $1557万
 $27,180/呎
-(22年-07月)</t>
+(22年-07月-31日)</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
@@ -15387,7 +20387,7 @@
           <t>F | 381呎 (1房)
 $744万
 $19,525/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
@@ -15395,7 +20395,7 @@
           <t>G | 380呎 (1房)
 $736万
 $19,361/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="I11" s="23" t="inlineStr">
@@ -15403,7 +20403,7 @@
           <t>H | 379呎 (1房)
 $743万
 $19,606/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
@@ -15411,7 +20411,7 @@
           <t>J | 414呎 (1房)
 $875万
 $21,135/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
     </row>
@@ -15426,7 +20426,7 @@
           <t>A | 888呎 (3房)
 $3215万
 $36,200/呎
-(24年-04月)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -15434,7 +20434,7 @@
           <t>B | 550呎 (2房)
 $1854万
 $33,700/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -15442,7 +20442,7 @@
           <t>C | 543呎 (2房)
 $1850万
 $34,062/呎
-(23年-04月)</t>
+(23年-04月-19日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -15450,7 +20450,7 @@
           <t>D | 479呎 (2房)
 $1493万
 $31,163/呎
-(23年-03月)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -15458,7 +20458,7 @@
           <t>E | 573呎 (2房)
 $1553万
 $27,101/呎
-(22年-08月)</t>
+(22年-08月-02日)</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
@@ -15466,7 +20466,7 @@
           <t>F | 381呎 (1房)
 $742万
 $19,473/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
@@ -15474,7 +20474,7 @@
           <t>G | 380呎 (1房)
 $734万
 $19,305/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
@@ -15482,7 +20482,7 @@
           <t>H | 379呎 (1房)
 $898万
 $23,697/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
@@ -15490,7 +20490,7 @@
           <t>J | 414呎 (1房)
 $872万
 $21,074/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -15505,7 +20505,7 @@
           <t>A | 888呎 (3房)
 $3189万
 $35,910/呎
-(23年-05月)</t>
+(23年-05月-15日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -15513,7 +20513,7 @@
           <t>B | 550呎 (2房)
 $1848万
 $33,600/呎
-(25年-02月)</t>
+(25年-02月-27日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -15521,7 +20521,7 @@
           <t>C | 543呎 (2房)
 $1844万
 $33,962/呎
-(23年-06月)</t>
+(23年-06月-28日)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -15529,7 +20529,7 @@
           <t>D | 479呎 (2房)
 $1488万
 $31,074/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -15537,7 +20537,7 @@
           <t>E | 573呎 (2房)
 $1383万
 $24,133/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
@@ -15545,7 +20545,7 @@
           <t>F | 381呎 (1房)
 $809万
 $21,246/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
@@ -15553,7 +20553,7 @@
           <t>G | 380呎 (1房)
 $732万
 $19,252/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -15561,7 +20561,7 @@
           <t>H | 379呎 (1房)
 $739万
 $19,492/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="J13" s="23" t="inlineStr">
@@ -15569,7 +20569,7 @@
           <t>J | 414呎 (1房)
 $870万
 $21,013/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
     </row>
@@ -15584,7 +20584,7 @@
           <t>A | 888呎 (3房)
 $3179万
 $35,800/呎
-(22年-06月)</t>
+(22年-06月-08日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -15592,7 +20592,7 @@
           <t>B | 550呎 (2房)
 $1842万
 $33,500/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -15600,7 +20600,7 @@
           <t>C | 543呎 (2房)
 $1839万
 $33,862/呎
-(23年-08月)</t>
+(23年-08月-28日)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -15608,7 +20608,7 @@
           <t>D | 479呎 (2房)
 $1547万
 $32,287/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
@@ -15616,7 +20616,7 @@
           <t>E | 575呎 (2房)
 $1497万
 $26,030/呎
-(22年-08月)</t>
+(22年-08月-10日)</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
@@ -15624,7 +20624,7 @@
           <t>F | 381呎 (1房)
 $807万
 $21,186/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
@@ -15632,7 +20632,7 @@
           <t>G | 380呎 (1房)
 $884万
 $23,268/呎
-(24年-12月)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
@@ -15640,7 +20640,7 @@
           <t>H | 379呎 (1房)
 $893万
 $23,560/呎
-(24年-12月)</t>
+(24年-12月-01日)</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
@@ -15648,7 +20648,7 @@
           <t>J | 414呎 (1房)
 $867万
 $20,949/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -15663,7 +20663,7 @@
           <t>A | 888呎 (3房)
 $3030万
 $34,122/呎
-(24年-12月)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -15671,7 +20671,7 @@
           <t>B | 550呎 (2房)
 $1837万
 $33,400/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -15679,7 +20679,7 @@
           <t>C | 543呎 (2房)
 $1833万
 $33,763/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -15687,7 +20687,7 @@
           <t>D | 479呎 (2房)
 $1480万
 $30,892/呎
-(25年-01月)</t>
+(25年-01月-19日)</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
@@ -15695,7 +20695,7 @@
           <t>E | 573呎 (2房)
 $1492万
 $26,045/呎
-(22年-08月)</t>
+(22年-08月-08日)</t>
         </is>
       </c>
       <c r="G15" s="23" t="inlineStr">
@@ -15703,7 +20703,7 @@
           <t>F | 381呎 (1房)
 $805万
 $21,126/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="H15" s="23" t="inlineStr">
@@ -15711,7 +20711,7 @@
           <t>G | 380呎 (1房)
 $727万
 $19,142/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="I15" s="23" t="inlineStr">
@@ -15719,7 +20719,7 @@
           <t>H | 379呎 (1房)
 $967万
 $25,504/呎
-(23年-04月)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="J15" s="23" t="inlineStr">
@@ -15727,7 +20727,7 @@
           <t>J | 414呎 (1房)
 $865万
 $20,886/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -15742,7 +20742,7 @@
           <t>A | 888呎 (3房)
 $3010万
 $33,896/呎
-(23年-10月)</t>
+(23年-10月-19日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -15750,7 +20750,7 @@
           <t>B | 550呎 (2房)
 $1832万
 $33,300/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -15758,7 +20758,7 @@
           <t>C | 543呎 (2房)
 $1905万
 $35,080/呎
-(22年-09月)</t>
+(22年-09月-15日)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -15766,7 +20766,7 @@
           <t>D | 476呎 (2房)
 $1475万
 $30,995/呎
-(23年-02月)</t>
+(23年-02月-20日)</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -15774,7 +20774,7 @@
           <t>E | 573呎 (2房)
 $1519万
 $26,515/呎
-(22年-08月)</t>
+(22年-08月-14日)</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
@@ -15782,7 +20782,7 @@
           <t>F | 381呎 (1房)
 $726万
 $19,050/呎
-(25年-06月)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
@@ -15790,7 +20790,7 @@
           <t>G | 380呎 (1房)
 $889万
 $23,399/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
@@ -15798,7 +20798,7 @@
           <t>H | 379呎 (1房)
 $964万
 $25,432/呎
-(22年-05月)</t>
+(22年-05月-16日)</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
@@ -15806,7 +20806,7 @@
           <t>J | 414呎 (1房)
 $862万
 $20,827/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -15821,7 +20821,7 @@
           <t>A | 888呎 (3房)
 $2948万
 $33,200/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -15829,7 +20829,7 @@
           <t>B | 550呎 (2房)
 $1820万
 $33,100/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -15837,7 +20837,7 @@
           <t>C | 543呎 (2房)
 $1817万
 $33,463/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -15845,7 +20845,7 @@
           <t>D | 479呎 (2房)
 $1467万
 $30,620/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -15853,7 +20853,7 @@
           <t>E | 573呎 (2房)
 $1557万
 $27,176/呎
-(22年-08月)</t>
+(22年-08月-14日)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -15861,7 +20861,7 @@
           <t>F | 381呎 (1房)
 $722万
 $18,938/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
@@ -15869,7 +20869,7 @@
           <t>G | 380呎 (1房)
 $797万
 $20,982/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="I17" s="23" t="inlineStr">
@@ -15877,7 +20877,7 @@
           <t>H | 379呎 (1房)
 $728万
 $19,213/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="J17" s="23" t="inlineStr">
@@ -15885,7 +20885,7 @@
           <t>J | 414呎 (1房)
 $775万
 $18,719/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -15900,7 +20900,7 @@
           <t>A | 888呎 (3房)
 $3019万
 $34,000/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -15908,7 +20908,7 @@
           <t>B | 550呎 (2房)
 $1815万
 $33,000/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -15916,7 +20916,7 @@
           <t>C | 543呎 (2房)
 $1812万
 $33,364/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -15924,7 +20924,7 @@
           <t>D | 479呎 (2房)
 $1462万
 $30,529/呎
-(23年-08月)</t>
+(23年-08月-13日)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -15932,7 +20932,7 @@
           <t>E | 573呎 (2房)
 $1553万
 $27,096/呎
-(22年-08月)</t>
+(22年-08月-07日)</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -15940,7 +20940,7 @@
           <t>F | 381呎 (1房)
 $719万
 $18,882/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
@@ -15948,7 +20948,7 @@
           <t>G | 380呎 (1房)
 $795万
 $20,922/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
@@ -15956,7 +20956,7 @@
           <t>H | 379呎 (1房)
 $880万
 $23,218/呎
-(25年-05月)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
@@ -15964,7 +20964,7 @@
           <t>J | 414呎 (1房)
 $773万
 $18,664/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -15979,7 +20979,7 @@
           <t>A | 888呎 (3房)
 $2984万
 $33,600/呎
-(25年-01月)</t>
+(25年-01月-05日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -15987,7 +20987,7 @@
           <t>B | 550呎 (2房)
 $1810万
 $32,900/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -15995,7 +20995,7 @@
           <t>C | 543呎 (2房)
 $1806万
 $33,266/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -16003,7 +21003,7 @@
           <t>D | 479呎 (2房)
 $1458万
 $30,440/呎
-(23年-02月)</t>
+(23年-02月-09日)</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -16011,7 +21011,7 @@
           <t>E | 575呎 (2房)
 $1471万
 $25,578/呎
-(22年-07月)</t>
+(22年-07月-31日)</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -16019,7 +21019,7 @@
           <t>F | 381呎 (1房)
 $717万
 $18,827/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
@@ -16027,7 +21027,7 @@
           <t>G | 380呎 (1房)
 $793万
 $20,859/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="I19" s="23" t="inlineStr">
@@ -16035,7 +21035,7 @@
           <t>H | 379呎 (1房)
 $724万
 $19,100/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="J19" s="23" t="inlineStr">
@@ -16043,7 +21043,7 @@
           <t>J | 414呎 (1房)
 $770万
 $18,607/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -16058,7 +21058,7 @@
           <t>A | 888呎 (3房)
 $3010万
 $33,900/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -16066,7 +21066,7 @@
           <t>B | 550呎 (2房)
 $1804万
 $32,800/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -16074,7 +21074,7 @@
           <t>C | 543呎 (2房)
 $1801万
 $33,166/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -16082,7 +21082,7 @@
           <t>D | 479呎 (2房)
 $1515万
 $31,626/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
@@ -16090,7 +21090,7 @@
           <t>E | 573呎 (2房)
 $1497万
 $26,125/呎
-(22年-08月)</t>
+(22年-08月-04日)</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
@@ -16098,7 +21098,7 @@
           <t>F | 381呎 (1房)
 $715万
 $18,772/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
@@ -16106,7 +21106,7 @@
           <t>G | 380呎 (1房)
 $790万
 $20,797/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
@@ -16114,7 +21114,7 @@
           <t>H | 379呎 (1房)
 $885万
 $23,346/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
@@ -16122,7 +21122,7 @@
           <t>J | 414呎 (1房)
 $768万
 $18,552/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -16137,7 +21137,7 @@
           <t>A | 888呎 (3房)
 $3038万
 $34,212/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -16145,7 +21145,7 @@
           <t>B | 550呎 (2房)
 $1798万
 $32,691/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -16153,7 +21153,7 @@
           <t>C | 543呎 (2房)
 $1796万
 $33,066/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -16161,7 +21161,7 @@
           <t>D | 479呎 (2房)
 $1465万
 $30,576/呎
-(23年-12月)</t>
+(23年-12月-28日)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -16169,7 +21169,7 @@
           <t>E | 575呎 (2房)
 $1447万
 $25,163/呎
-(22年-07月)</t>
+(22年-07月-31日)</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -16177,7 +21177,7 @@
           <t>F | 381呎 (1房)
 $713万
 $18,717/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
@@ -16185,7 +21185,7 @@
           <t>G | 380呎 (1房)
 $788万
 $20,740/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -16193,7 +21193,7 @@
           <t>H | 379呎 (1房)
 $732万
 $19,312/呎
-(25年-06月)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="J21" s="23" t="inlineStr">
@@ -16201,7 +21201,7 @@
           <t>J | 414呎 (1房)
 $779万
 $18,814/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
     </row>
@@ -16216,7 +21216,7 @@
           <t>A | 888呎 (3房)
 $3110万
 $35,023/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -16224,7 +21224,7 @@
           <t>B | 550呎 (2房)
 $1886万
 $34,300/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -16240,7 +21240,7 @@
           <t>D | 479呎 (2房)
 $1447万
 $30,210/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
@@ -16248,7 +21248,7 @@
           <t>E | 575呎 (2房)
 $1443万
 $25,088/呎
-(22年-08月)</t>
+(22年-08月-07日)</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
@@ -16256,7 +21256,7 @@
           <t>F | 381呎 (1房)
 $711万
 $18,662/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
@@ -16264,7 +21264,7 @@
           <t>G | 380呎 (1房)
 $786万
 $20,675/呎
-(25年-08月)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -16272,7 +21272,7 @@
           <t>H | 379呎 (1房)
 $895万
 $23,604/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
@@ -16280,7 +21280,7 @@
           <t>J | 414呎 (1房)
 $763万
 $18,438/呎
-(25年-06月)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -16295,7 +21295,7 @@
           <t>A | 888呎 (3房)
 $2940万
 $33,108/呎
-(25年-08月)</t>
+(25年-08月-05日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -16303,7 +21303,7 @@
           <t>B | 550呎 (2房)
 $1741万
 $31,655/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -16311,7 +21311,7 @@
           <t>C | 543呎 (2房)
 $1742万
 $32,081/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -16319,7 +21319,7 @@
           <t>D | 479呎 (2房)
 $1443万
 $30,121/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
@@ -16327,7 +21327,7 @@
           <t>E | 575呎 (2房)
 $1453万
 $25,275/呎
-(22年-07月)</t>
+(22年-07月-26日)</t>
         </is>
       </c>
       <c r="G23" s="23" t="inlineStr">
@@ -16335,7 +21335,7 @@
           <t>F | 381呎 (1房)
 $933万
 $24,486/呎
-(23年-05月)</t>
+(23年-05月-02日)</t>
         </is>
       </c>
       <c r="H23" s="23" t="inlineStr">
@@ -16343,7 +21343,7 @@
           <t>G | 380呎 (1房)
 $932万
 $24,532/呎
-(23年-02月)</t>
+(23年-02月-01日)</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
@@ -16351,7 +21351,7 @@
           <t>H | 379呎 (1房)
 $951万
 $25,102/呎
-(22年-06月)</t>
+(22年-06月-16日)</t>
         </is>
       </c>
       <c r="J23" s="23" t="inlineStr">
@@ -16359,7 +21359,7 @@
           <t>J | 414呎 (1房)
 $842万
 $20,330/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
     </row>
@@ -16374,7 +21374,7 @@
           <t>A | 888呎 (3房)
 $2939万
 $33,100/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -16390,7 +21390,7 @@
           <t>C | 542呎 (2房)
 $1808万
 $33,358/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -16398,7 +21398,7 @@
           <t>D | 479呎 (2房)
 $1438万
 $30,011/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -16406,7 +21406,7 @@
           <t>E | 573呎 (2房)
 $1479万
 $25,819/呎
-(22年-08月)</t>
+(22年-08月-22日)</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
@@ -16414,7 +21414,7 @@
           <t>F | 381呎 (1房)
 $960万
 $25,184/呎
-(22年-07月)</t>
+(22年-07月-25日)</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
@@ -16422,7 +21422,7 @@
           <t>G | 380呎 (1房)
 $949万
 $24,975/呎
-(22年-08月)</t>
+(22年-08月-11日)</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -16430,7 +21430,7 @@
           <t>H | 379呎 (1房)
 $949万
 $25,028/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
@@ -16438,7 +21438,7 @@
           <t>J | 414呎 (1房)
 $839万
 $20,266/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -16453,7 +21453,7 @@
           <t>A | 888呎 (3房)
 $2930万
 $33,000/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -16485,7 +21485,7 @@
           <t>E | 573呎 (2房)
 $1328万
 $23,176/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
@@ -16493,7 +21493,7 @@
           <t>F | 381呎 (1房)
 $715万
 $18,764/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
@@ -16501,7 +21501,7 @@
           <t>G | 380呎 (1房)
 $969万
 $25,490/呎
-(22年-09月)</t>
+(22年-09月-05日)</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -16509,7 +21509,7 @@
           <t>H | 379呎 (1房)
 $939万
 $24,768/呎
-(22年-06月)</t>
+(22年-06月-08日)</t>
         </is>
       </c>
       <c r="J25" s="23" t="inlineStr">
@@ -16517,7 +21517,7 @@
           <t>J | 414呎 (1房)
 $839万
 $20,266/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -16532,7 +21532,7 @@
           <t>A | 888呎 (3房)
 $2930万
 $32,995/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -16564,7 +21564,7 @@
           <t>E | 573呎 (2房)
 $1505万
 $26,272/呎
-(22年-08月)</t>
+(22年-08月-24日)</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
@@ -16572,7 +21572,7 @@
           <t>F | 381呎 (1房)
 $705万
 $18,497/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H26" s="23" t="inlineStr">
@@ -16580,7 +21580,7 @@
           <t>G | 380呎 (1房)
 $936万
 $24,644/呎
-(23年-01月)</t>
+(23年-01月-25日)</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
@@ -16588,7 +21588,7 @@
           <t>H | 379呎 (1房)
 $936万
 $24,692/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
@@ -16596,7 +21596,7 @@
           <t>J | 414呎 (1房)
 $836万
 $20,205/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -16611,7 +21611,7 @@
           <t>A | 888呎 (3房)
 $2920万
 $32,883/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -16627,7 +21627,7 @@
           <t>C | 543呎 (2房)
 $1772万
 $32,640/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -16643,7 +21643,7 @@
           <t>E | 573呎 (2房)
 $1440万
 $25,136/呎
-(22年-08月)</t>
+(22年-08月-28日)</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
@@ -16651,7 +21651,7 @@
           <t>F | 381呎 (1房)
 $703万
 $18,441/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="H27" s="23" t="inlineStr">
@@ -16659,7 +21659,7 @@
           <t>G | 380呎 (1房)
 $924万
 $24,315/呎
-(23年-04月)</t>
+(23年-04月-19日)</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -16667,7 +21667,7 @@
           <t>H | 379呎 (1房)
 $933万
 $24,605/呎
-(22年-05月)</t>
+(22年-05月-18日)</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
@@ -16675,7 +21675,7 @@
           <t>J | 414呎 (1房)
 $914万
 $22,080/呎
-(25年-04月)</t>
+(25年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -16690,7 +21690,7 @@
           <t>A | 888呎 (3房)
 $2913万
 $32,800/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -16698,7 +21698,7 @@
           <t>B | 550呎 (2房)
 $1766万
 $32,100/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -16706,7 +21706,7 @@
           <t>C | 543呎 (2房)
 $1767万
 $32,540/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -16722,7 +21722,7 @@
           <t>E | 573呎 (2房)
 $1436万
 $25,060/呎
-(22年-09月)</t>
+(22年-09月-12日)</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -16730,7 +21730,7 @@
           <t>F | 381呎 (1房)
 $701万
 $18,386/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
@@ -16738,7 +21738,7 @@
           <t>G | 380呎 (1房)
 $700万
 $18,421/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
@@ -16746,7 +21746,7 @@
           <t>H | 379呎 (1房)
 $931万
 $24,560/呎
-(22年-05月)</t>
+(22年-05月-25日)</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
@@ -16754,7 +21754,7 @@
           <t>J | 414呎 (1房)
 $911万
 $22,012/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -16769,7 +21769,7 @@
           <t>A | 888呎 (3房)
 $2904万
 $32,700/呎
-(25年-08月)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -16785,7 +21785,7 @@
           <t>C | 543呎 (2房)
 $1789万
 $32,939/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -16801,7 +21801,7 @@
           <t>E | 573呎 (2房)
 $1497万
 $26,134/呎
-(22年-10月)</t>
+(22年-10月-26日)</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
@@ -16809,7 +21809,7 @@
           <t>F | 381呎 (1房)
 $739万
 $19,392/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
@@ -16817,7 +21817,7 @@
           <t>G | 380呎 (1房)
 $738万
 $19,429/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
@@ -16825,7 +21825,7 @@
           <t>H | 379呎 (1房)
 $745万
 $19,661/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
@@ -16833,7 +21833,7 @@
           <t>J | 414呎 (1房)
 $794万
 $19,167/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -16848,7 +21848,7 @@
           <t>A | 888呎 (3房)
 $2859万
 $32,200/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -16880,7 +21880,7 @@
           <t>E | 575呎 (2房)
 $1423万
 $24,748/呎
-(22年-05月)</t>
+(22年-05月-16日)</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -16888,7 +21888,7 @@
           <t>F | 381呎 (1房)
 $914万
 $23,977/呎
-(22年-07月)</t>
+(22年-07月-28日)</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
@@ -16896,7 +21896,7 @@
           <t>G | 380呎 (1房)
 $694万
 $18,253/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
@@ -16904,7 +21904,7 @@
           <t>H | 379呎 (1房)
 $922万
 $24,324/呎
-(22年-11月)</t>
+(22年-11月-06日)</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
@@ -16912,7 +21912,7 @@
           <t>J | 414呎 (1房)
 $745万
 $17,990/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -16927,7 +21927,7 @@
           <t>A | 888呎 (3房)
 $2895万
 $32,600/呎
-(26年-06月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -16935,7 +21935,7 @@
           <t>B | 550呎 (2房)
 $1678万
 $30,509/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -16943,7 +21943,7 @@
           <t>C | 543呎 (2房)
 $1729万
 $31,841/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -16959,7 +21959,7 @@
           <t>E | 573呎 (2房)
 $1463万
 $25,531/呎
-(22年-09月)</t>
+(22年-09月-14日)</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
@@ -16967,7 +21967,7 @@
           <t>F | 381呎 (1房)
 $911万
 $23,904/呎
-(22年-10月)</t>
+(22年-10月-10日)</t>
         </is>
       </c>
       <c r="H31" s="23" t="inlineStr">
@@ -16975,7 +21975,7 @@
           <t>G | 380呎 (1房)
 $692万
 $18,200/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
@@ -16983,7 +21983,7 @@
           <t>H | 379呎 (1房)
 $919万
 $24,249/呎
-(23年-01月)</t>
+(23年-01月-31日)</t>
         </is>
       </c>
       <c r="J31" s="23" t="inlineStr">
@@ -16991,7 +21991,7 @@
           <t>J | 414呎 (1房)
 $900万
 $21,740/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -17006,7 +22006,7 @@
           <t>A | 888呎 (3房)
 $2895万
 $32,600/呎
-(26年-06月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -17014,7 +22014,7 @@
           <t>B | 550呎 (2房)
 $1754万
 $31,900/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -17022,7 +22022,7 @@
           <t>C | 542呎 (2房)
 $1756万
 $32,400/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -17038,7 +22038,7 @@
           <t>E | 573呎 (2房)
 $1463万
 $25,531/呎
-(22年-09月)</t>
+(22年-09月-21日)</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
@@ -17046,7 +22046,7 @@
           <t>F | 381呎 (1房)
 $692万
 $18,164/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H32" s="23" t="inlineStr">
@@ -17054,7 +22054,7 @@
           <t>G | 380呎 (1房)
 $692万
 $18,200/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
@@ -17062,7 +22062,7 @@
           <t>H | 379呎 (1房)
 $698万
 $18,426/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="J32" s="23" t="inlineStr">
@@ -17070,7 +22070,7 @@
           <t>J | 414呎 (1房)
 $743万
 $17,935/呎
-(25年-06月)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -17093,7 +22093,7 @@
           <t>B | 550呎 (2房)
 $1704万
 $30,982/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -17101,7 +22101,7 @@
           <t>C | 542呎 (2房)
 $1704万
 $31,439/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -17117,7 +22117,7 @@
           <t>E | 573呎 (2房)
 $1400万
 $24,433/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr">
@@ -17125,7 +22125,7 @@
           <t>F | 381呎 (1房)
 $690万
 $18,108/呎
-(25年-06月)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="H33" s="23" t="inlineStr">
@@ -17133,7 +22133,7 @@
           <t>G | 380呎 (1房)
 $690万
 $18,145/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="I33" s="23" t="inlineStr">
@@ -17141,7 +22141,7 @@
           <t>H | 379呎 (1房)
 $696万
 $18,370/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="J33" s="23" t="inlineStr">
@@ -17149,7 +22149,7 @@
           <t>J | 414呎 (1房)
 $740万
 $17,880/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -17164,7 +22164,7 @@
           <t>A | 888呎 (3房)
 $2877万
 $32,400/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -17196,7 +22196,7 @@
           <t>E | 573呎 (2房)
 $1445万
 $25,218/呎
-(22年-09月)</t>
+(22年-09月-28日)</t>
         </is>
       </c>
       <c r="G34" s="23" t="inlineStr">
@@ -17204,7 +22204,7 @@
           <t>F | 381呎 (1房)
 $704万
 $18,487/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="H34" s="23" t="inlineStr">
@@ -17212,7 +22212,7 @@
           <t>G | 380呎 (1房)
 $732万
 $19,263/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="I34" s="23" t="inlineStr">
@@ -17220,7 +22220,7 @@
           <t>H | 379呎 (1房)
 $841万
 $22,198/呎
-(24年-08月)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
       <c r="J34" s="23" t="inlineStr">
@@ -17228,7 +22228,7 @@
           <t>J | 414呎 (1房)
 $895万
 $21,607/呎
-(24年-08月)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
     </row>
@@ -17275,7 +22275,7 @@
           <t>E | 573呎 (2房)
 $1432万
 $24,985/呎
-(22年-10月)</t>
+(22年-10月-19日)</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr">
@@ -17283,7 +22283,7 @@
           <t>F | 381呎 (1房)
 $698万
 $18,318/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="H35" s="23" t="inlineStr">
@@ -17291,7 +22291,7 @@
           <t>G | 380呎 (1房)
 $697万
 $18,352/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="I35" s="23" t="inlineStr">
@@ -17299,7 +22299,7 @@
           <t>H | 379呎 (1房)
 $713万
 $18,811/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="J35" s="23" t="inlineStr">
@@ -17307,7 +22307,7 @@
           <t>J | 414呎 (1房)
 $813万
 $19,647/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
     </row>
@@ -17354,7 +22354,7 @@
           <t>E | 573呎 (2房)
 $1369万
 $23,899/呎
-(23年-01月)</t>
+(23年-01月-08日)</t>
         </is>
       </c>
       <c r="G36" s="23" t="inlineStr">
@@ -17362,7 +22362,7 @@
           <t>F | 381呎 (1房)
 $696万
 $18,260/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="H36" s="23" t="inlineStr">
@@ -17370,7 +22370,7 @@
           <t>G | 380呎 (1房)
 $897万
 $23,613/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="I36" s="23" t="inlineStr">
@@ -17378,7 +22378,7 @@
           <t>H | 379呎 (1房)
 $711万
 $18,754/呎
-(25年-06月)</t>
+(25年-06月-06日)</t>
         </is>
       </c>
       <c r="J36" s="23" t="inlineStr">
@@ -17386,7 +22386,7 @@
           <t>J | 414呎 (1房)
 $811万
 $19,586/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -17433,7 +22433,7 @@
           <t>E | 573呎 (2房)
 $1390万
 $24,250/呎
-(22年-08月)</t>
+(22年-08月-16日)</t>
         </is>
       </c>
       <c r="G37" s="23" t="inlineStr">
@@ -17441,7 +22441,7 @@
           <t>F | 381呎 (1房)
 $691万
 $18,148/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="H37" s="23" t="inlineStr">
@@ -17449,7 +22449,7 @@
           <t>G | 380呎 (1房)
 $920万
 $24,200/呎
-(22年-08月)</t>
+(22年-08月-21日)</t>
         </is>
       </c>
       <c r="I37" s="23" t="inlineStr">
@@ -17457,7 +22457,7 @@
           <t>H | 379呎 (1房)
 $706万
 $18,638/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="J37" s="23" t="inlineStr">
@@ -17465,7 +22465,7 @@
           <t>J | 414呎 (1房)
 $806万
 $19,461/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
     </row>
@@ -17491,7 +22491,7 @@
           <t>E | 573呎 (2房)
 $1376万
 $24,020/呎
-(23年-02月)</t>
+(23年-02月-16日)</t>
         </is>
       </c>
       <c r="G38" s="23" t="inlineStr">
@@ -17499,7 +22499,7 @@
           <t>F | 381呎 (1房)
 $685万
 $17,969/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="H38" s="23" t="inlineStr">
@@ -17507,7 +22507,7 @@
           <t>G | 380呎 (1房)
 $684万
 $18,002/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="I38" s="23" t="inlineStr">
@@ -17515,7 +22515,7 @@
           <t>H | 379呎 (1房)
 $702万
 $18,523/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="J38" s="23" t="inlineStr">
@@ -17523,7 +22523,7 @@
           <t>J | 414呎 (1房)
 $801万
 $19,336/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-The Henley II.xlsx
+++ b/files/九龙-启德-The Henley II.xlsx
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
@@ -16262,14 +16262,14 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
         <v>17560800</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>32400</v>
+        <v>32340</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>17560800</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>32400</v>
+        <v>32340</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="E259" s="4" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
@@ -16828,14 +16828,14 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
         <v>17040000</v>
       </c>
       <c r="I259" s="5" t="n">
-        <v>31439</v>
+        <v>31381</v>
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>17040000</v>
       </c>
       <c r="L259" s="5" t="n">
-        <v>31439</v>
+        <v>31381</v>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
@@ -22014,15 +22014,15 @@
           <t>B | 550呎 (2房)
 $1754万
 $31,900/呎
-(26年-06月-09日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>C | 542呎 (2房)
+          <t>C | 543呎 (2房)
 $1756万
-$32,400/呎
-(26年-06月-09日)</t>
+$32,340/呎
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -22098,10 +22098,10 @@
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>C | 542呎 (2房)
+          <t>C | 543呎 (2房)
 $1704万
-$31,439/呎
-(26年-06月-10日)</t>
+$31,381/呎
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">

--- a/files/九龙-启德-The Henley II.xlsx
+++ b/files/九龙-启德-The Henley II.xlsx
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="E178" s="4" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>18080000</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>33358</v>
+        <v>33297</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>18080000</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>33358</v>
+        <v>33297</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
@@ -12161,38 +12161,30 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H186" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I186" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H186" s="5" t="n">
+        <v>14613200</v>
+      </c>
+      <c r="I186" s="5" t="n">
+        <v>30700</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K186" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L186" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K186" s="5" t="n">
+        <v>14613200</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>30700</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
@@ -12201,7 +12193,7 @@
       </c>
       <c r="N186" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -19800,7 +19792,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -19810,7 +19802,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -21387,9 +21379,9 @@
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>C | 542呎 (2房)
+          <t>C | 543呎 (2房)
 $1808万
-$33,358/呎
+$33,297/呎
 (26年-07月-02日)</t>
         </is>
       </c>
@@ -21472,12 +21464,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
-招标单位
--
-(在售)</t>
+$1461万
+$30,700/呎
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">

--- a/files/九龙-启德-The Henley II.xlsx
+++ b/files/九龙-启德-The Henley II.xlsx
@@ -19897,7 +19897,7 @@
           <t>E | 573呎 (2房)
 $2108万
 $36,789/呎
-(22年-11月-07日)</t>
+(22年-11月)</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
@@ -19905,7 +19905,7 @@
           <t>F | 381呎 (1房)
 $859万
 $22,546/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
@@ -19913,7 +19913,7 @@
           <t>G | 380呎 (1房)
 $858万
 $22,589/呎
-(26年-01月-20日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -19944,7 +19944,7 @@
           <t>A | 888呎 (3房)
 $3163万
 $35,618/呎
-(25年-04月-01日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -19952,7 +19952,7 @@
           <t>B | 550呎 (2房)
 $1908万
 $34,700/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -19960,7 +19960,7 @@
           <t>C | 543呎 (2房)
 $1908万
 $35,135/呎
-(25年-11月-20日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -19968,7 +19968,7 @@
           <t>D | 479呎 (2房)
 $1533万
 $31,998/呎
-(25年-05月-27日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -19976,7 +19976,7 @@
           <t>E | 573呎 (2房)
 $1569万
 $27,381/呎
-(23年-06月-22日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
@@ -19984,7 +19984,7 @@
           <t>F | 381呎 (1房)
 $835万
 $21,919/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -19992,7 +19992,7 @@
           <t>G | 380呎 (1房)
 $835万
 $21,962/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
@@ -20000,7 +20000,7 @@
           <t>H | 379呎 (1房)
 $834万
 $22,009/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
@@ -20008,7 +20008,7 @@
           <t>J | 414呎 (1房)
 $919万
 $22,191/呎
-(26年-01月-04日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -20023,7 +20023,7 @@
           <t>A | 888呎 (3房)
 $3450万
 $38,851/呎
-(22年-05月-23日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -20031,7 +20031,7 @@
           <t>B | 550呎 (2房)
 $1886万
 $34,300/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -20039,7 +20039,7 @@
           <t>C | 543呎 (2房)
 $1886万
 $34,736/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -20047,7 +20047,7 @@
           <t>D | 479呎 (2房)
 $1523万
 $31,800/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -20055,7 +20055,7 @@
           <t>E | 575呎 (2房)
 $1548万
 $26,915/呎
-(22年-05月-17日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -20063,7 +20063,7 @@
           <t>F | 381呎 (1房)
 $755万
 $19,806/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
@@ -20071,7 +20071,7 @@
           <t>G | 380呎 (1房)
 $825万
 $21,718/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
@@ -20079,7 +20079,7 @@
           <t>H | 379呎 (1房)
 $825万
 $21,762/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
@@ -20087,7 +20087,7 @@
           <t>J | 414呎 (1房)
 $898万
 $21,691/呎
-(25年-08月-07日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -20102,7 +20102,7 @@
           <t>A | 888呎 (3房)
 $3313万
 $37,309/呎
-(23年-11月-30日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -20110,7 +20110,7 @@
           <t>B | 550呎 (2房)
 $1876万
 $34,100/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -20118,7 +20118,7 @@
           <t>C | 543呎 (2房)
 $1873万
 $34,490/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -20126,7 +20126,7 @@
           <t>D | 479呎 (2房)
 $1553万
 $32,412/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -20134,7 +20134,7 @@
           <t>E | 575呎 (2房)
 $1523万
 $26,483/呎
-(22年-07月-21日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -20142,7 +20142,7 @@
           <t>F | 381呎 (1房)
 $750万
 $19,696/呎
-(25年-06月-29日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -20150,7 +20150,7 @@
           <t>G | 380呎 (1房)
 $821万
 $21,596/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
@@ -20158,7 +20158,7 @@
           <t>H | 379呎 (1房)
 $820万
 $21,639/呎
-(25年-11月-03日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
@@ -20166,7 +20166,7 @@
           <t>J | 414呎 (1房)
 $903万
 $21,808/呎
-(26年-01月-07日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -20181,7 +20181,7 @@
           <t>A | 888呎 (3房)
 $3081万
 $34,700/呎
-(25年-02月-10日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -20189,7 +20189,7 @@
           <t>B | 550呎 (2房)
 $1870万
 $34,000/呎
-(26年-01月-22日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -20197,7 +20197,7 @@
           <t>C | 543呎 (2房)
 $1866万
 $34,359/呎
-(23年-06月-11日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -20205,7 +20205,7 @@
           <t>D | 479呎 (2房)
 $1506万
 $31,435/呎
-(25年-02月-05日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -20213,7 +20213,7 @@
           <t>E | 573呎 (2房)
 $1518万
 $26,499/呎
-(22年-07月-24日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
@@ -20221,7 +20221,7 @@
           <t>F | 381呎 (1房)
 $748万
 $19,638/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
@@ -20229,7 +20229,7 @@
           <t>G | 380呎 (1房)
 $818万
 $21,534/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -20237,7 +20237,7 @@
           <t>H | 379呎 (1房)
 $818万
 $21,579/呎
-(25年-10月-21日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr">
@@ -20245,7 +20245,7 @@
           <t>J | 414呎 (1房)
 $880万
 $21,260/呎
-(25年-10月-21日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -20260,7 +20260,7 @@
           <t>A | 888呎 (3房)
 $3072万
 $34,600/呎
-(25年-03月-06日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -20268,7 +20268,7 @@
           <t>B | 550呎 (2房)
 $1864万
 $33,900/呎
-(26年-01月-07日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -20276,7 +20276,7 @@
           <t>C | 543呎 (2房)
 $1958万
 $36,063/呎
-(22年-10月-26日)</t>
+(22年-10月)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -20284,7 +20284,7 @@
           <t>D | 479呎 (2房)
 $1580万
 $32,996/呎
-(22年-09月-04日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -20292,7 +20292,7 @@
           <t>E | 573呎 (2房)
 $1546万
 $26,980/呎
-(22年-07月-27日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
@@ -20300,7 +20300,7 @@
           <t>F | 381呎 (1房)
 $746万
 $19,583/呎
-(25年-06月-25日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -20308,7 +20308,7 @@
           <t>G | 380呎 (1房)
 $738万
 $19,418/呎
-(25年-06月-17日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
@@ -20316,7 +20316,7 @@
           <t>H | 379呎 (1房)
 $745万
 $19,661/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
@@ -20324,7 +20324,7 @@
           <t>J | 414呎 (1房)
 $878万
 $21,196/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -20339,7 +20339,7 @@
           <t>A | 888呎 (3房)
 $3260万
 $36,712/呎
-(22年-05月-17日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -20347,7 +20347,7 @@
           <t>B | 550呎 (2房)
 $1859万
 $33,800/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -20355,7 +20355,7 @@
           <t>C | 542呎 (2房)
 $1855万
 $34,225/呎
-(22年-12月-18日)</t>
+(22年-12月)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -20363,7 +20363,7 @@
           <t>D | 479呎 (2房)
 $1497万
 $31,255/呎
-(23年-01月-09日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
@@ -20371,7 +20371,7 @@
           <t>E | 573呎 (2房)
 $1557万
 $27,180/呎
-(22年-07月-31日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
@@ -20379,7 +20379,7 @@
           <t>F | 381呎 (1房)
 $744万
 $19,525/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
@@ -20387,7 +20387,7 @@
           <t>G | 380呎 (1房)
 $736万
 $19,361/呎
-(25年-06月-17日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I11" s="23" t="inlineStr">
@@ -20395,7 +20395,7 @@
           <t>H | 379呎 (1房)
 $743万
 $19,606/呎
-(25年-06月-26日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
@@ -20403,7 +20403,7 @@
           <t>J | 414呎 (1房)
 $875万
 $21,135/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -20418,7 +20418,7 @@
           <t>A | 888呎 (3房)
 $3215万
 $36,200/呎
-(24年-04月-28日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -20426,7 +20426,7 @@
           <t>B | 550呎 (2房)
 $1854万
 $33,700/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -20434,7 +20434,7 @@
           <t>C | 543呎 (2房)
 $1850万
 $34,062/呎
-(23年-04月-19日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -20442,7 +20442,7 @@
           <t>D | 479呎 (2房)
 $1493万
 $31,163/呎
-(23年-03月-20日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -20450,7 +20450,7 @@
           <t>E | 573呎 (2房)
 $1553万
 $27,101/呎
-(22年-08月-02日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
@@ -20458,7 +20458,7 @@
           <t>F | 381呎 (1房)
 $742万
 $19,473/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
@@ -20466,7 +20466,7 @@
           <t>G | 380呎 (1房)
 $734万
 $19,305/呎
-(25年-06月-15日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
@@ -20474,7 +20474,7 @@
           <t>H | 379呎 (1房)
 $898万
 $23,697/呎
-(24年-11月-28日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
@@ -20482,7 +20482,7 @@
           <t>J | 414呎 (1房)
 $872万
 $21,074/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -20497,7 +20497,7 @@
           <t>A | 888呎 (3房)
 $3189万
 $35,910/呎
-(23年-05月-15日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -20505,7 +20505,7 @@
           <t>B | 550呎 (2房)
 $1848万
 $33,600/呎
-(25年-02月-27日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -20513,7 +20513,7 @@
           <t>C | 543呎 (2房)
 $1844万
 $33,962/呎
-(23年-06月-28日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -20521,7 +20521,7 @@
           <t>D | 479呎 (2房)
 $1488万
 $31,074/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -20529,7 +20529,7 @@
           <t>E | 573呎 (2房)
 $1383万
 $24,133/呎
-(25年-04月-22日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
@@ -20537,7 +20537,7 @@
           <t>F | 381呎 (1房)
 $809万
 $21,246/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
@@ -20545,7 +20545,7 @@
           <t>G | 380呎 (1房)
 $732万
 $19,252/呎
-(25年-06月-24日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -20553,7 +20553,7 @@
           <t>H | 379呎 (1房)
 $739万
 $19,492/呎
-(25年-06月-29日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J13" s="23" t="inlineStr">
@@ -20561,7 +20561,7 @@
           <t>J | 414呎 (1房)
 $870万
 $21,013/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -20576,7 +20576,7 @@
           <t>A | 888呎 (3房)
 $3179万
 $35,800/呎
-(22年-06月-08日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -20584,7 +20584,7 @@
           <t>B | 550呎 (2房)
 $1842万
 $33,500/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -20592,7 +20592,7 @@
           <t>C | 543呎 (2房)
 $1839万
 $33,862/呎
-(23年-08月-28日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -20600,7 +20600,7 @@
           <t>D | 479呎 (2房)
 $1547万
 $32,287/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
@@ -20608,7 +20608,7 @@
           <t>E | 575呎 (2房)
 $1497万
 $26,030/呎
-(22年-08月-10日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
@@ -20616,7 +20616,7 @@
           <t>F | 381呎 (1房)
 $807万
 $21,186/呎
-(25年-10月-29日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
@@ -20624,7 +20624,7 @@
           <t>G | 380呎 (1房)
 $884万
 $23,268/呎
-(24年-12月-04日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
@@ -20632,7 +20632,7 @@
           <t>H | 379呎 (1房)
 $893万
 $23,560/呎
-(24年-12月-01日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
@@ -20640,7 +20640,7 @@
           <t>J | 414呎 (1房)
 $867万
 $20,949/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -20655,7 +20655,7 @@
           <t>A | 888呎 (3房)
 $3030万
 $34,122/呎
-(24年-12月-19日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -20663,7 +20663,7 @@
           <t>B | 550呎 (2房)
 $1837万
 $33,400/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -20671,7 +20671,7 @@
           <t>C | 543呎 (2房)
 $1833万
 $33,763/呎
-(25年-02月-09日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -20679,7 +20679,7 @@
           <t>D | 479呎 (2房)
 $1480万
 $30,892/呎
-(25年-01月-19日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
@@ -20687,7 +20687,7 @@
           <t>E | 573呎 (2房)
 $1492万
 $26,045/呎
-(22年-08月-08日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="G15" s="23" t="inlineStr">
@@ -20695,7 +20695,7 @@
           <t>F | 381呎 (1房)
 $805万
 $21,126/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H15" s="23" t="inlineStr">
@@ -20703,7 +20703,7 @@
           <t>G | 380呎 (1房)
 $727万
 $19,142/呎
-(25年-06月-15日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I15" s="23" t="inlineStr">
@@ -20711,7 +20711,7 @@
           <t>H | 379呎 (1房)
 $967万
 $25,504/呎
-(23年-04月-27日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="J15" s="23" t="inlineStr">
@@ -20719,7 +20719,7 @@
           <t>J | 414呎 (1房)
 $865万
 $20,886/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -20734,7 +20734,7 @@
           <t>A | 888呎 (3房)
 $3010万
 $33,896/呎
-(23年-10月-19日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -20742,7 +20742,7 @@
           <t>B | 550呎 (2房)
 $1832万
 $33,300/呎
-(26年-01月-28日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -20750,7 +20750,7 @@
           <t>C | 543呎 (2房)
 $1905万
 $35,080/呎
-(22年-09月-15日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -20758,7 +20758,7 @@
           <t>D | 476呎 (2房)
 $1475万
 $30,995/呎
-(23年-02月-20日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -20766,7 +20766,7 @@
           <t>E | 573呎 (2房)
 $1519万
 $26,515/呎
-(22年-08月-14日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
@@ -20774,7 +20774,7 @@
           <t>F | 381呎 (1房)
 $726万
 $19,050/呎
-(25年-06月-11日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
@@ -20782,7 +20782,7 @@
           <t>G | 380呎 (1房)
 $889万
 $23,399/呎
-(25年-02月-11日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
@@ -20790,7 +20790,7 @@
           <t>H | 379呎 (1房)
 $964万
 $25,432/呎
-(22年-05月-16日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
@@ -20798,7 +20798,7 @@
           <t>J | 414呎 (1房)
 $862万
 $20,827/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -20813,7 +20813,7 @@
           <t>A | 888呎 (3房)
 $2948万
 $33,200/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -20821,7 +20821,7 @@
           <t>B | 550呎 (2房)
 $1820万
 $33,100/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -20829,7 +20829,7 @@
           <t>C | 543呎 (2房)
 $1817万
 $33,463/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -20837,7 +20837,7 @@
           <t>D | 479呎 (2房)
 $1467万
 $30,620/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -20845,7 +20845,7 @@
           <t>E | 573呎 (2房)
 $1557万
 $27,176/呎
-(22年-08月-14日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -20853,7 +20853,7 @@
           <t>F | 381呎 (1房)
 $722万
 $18,938/呎
-(25年-06月-15日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
@@ -20861,7 +20861,7 @@
           <t>G | 380呎 (1房)
 $797万
 $20,982/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="I17" s="23" t="inlineStr">
@@ -20869,7 +20869,7 @@
           <t>H | 379呎 (1房)
 $728万
 $19,213/呎
-(25年-06月-23日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J17" s="23" t="inlineStr">
@@ -20877,7 +20877,7 @@
           <t>J | 414呎 (1房)
 $775万
 $18,719/呎
-(25年-06月-23日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -20892,7 +20892,7 @@
           <t>A | 888呎 (3房)
 $3019万
 $34,000/呎
-(22年-05月-17日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -20900,7 +20900,7 @@
           <t>B | 550呎 (2房)
 $1815万
 $33,000/呎
-(26年-01月-04日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -20908,7 +20908,7 @@
           <t>C | 543呎 (2房)
 $1812万
 $33,364/呎
-(25年-05月-20日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -20916,7 +20916,7 @@
           <t>D | 479呎 (2房)
 $1462万
 $30,529/呎
-(23年-08月-13日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -20924,7 +20924,7 @@
           <t>E | 573呎 (2房)
 $1553万
 $27,096/呎
-(22年-08月-07日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -20932,7 +20932,7 @@
           <t>F | 381呎 (1房)
 $719万
 $18,882/呎
-(25年-06月-15日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
@@ -20940,7 +20940,7 @@
           <t>G | 380呎 (1房)
 $795万
 $20,922/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
@@ -20948,7 +20948,7 @@
           <t>H | 379呎 (1房)
 $880万
 $23,218/呎
-(25年-05月-26日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
@@ -20956,7 +20956,7 @@
           <t>J | 414呎 (1房)
 $773万
 $18,664/呎
-(25年-06月-15日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -20971,7 +20971,7 @@
           <t>A | 888呎 (3房)
 $2984万
 $33,600/呎
-(25年-01月-05日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -20979,7 +20979,7 @@
           <t>B | 550呎 (2房)
 $1810万
 $32,900/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -20987,7 +20987,7 @@
           <t>C | 543呎 (2房)
 $1806万
 $33,266/呎
-(23年-06月-11日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -20995,7 +20995,7 @@
           <t>D | 479呎 (2房)
 $1458万
 $30,440/呎
-(23年-02月-09日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -21003,7 +21003,7 @@
           <t>E | 575呎 (2房)
 $1471万
 $25,578/呎
-(22年-07月-31日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -21011,7 +21011,7 @@
           <t>F | 381呎 (1房)
 $717万
 $18,827/呎
-(25年-06月-17日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
@@ -21019,7 +21019,7 @@
           <t>G | 380呎 (1房)
 $793万
 $20,859/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="I19" s="23" t="inlineStr">
@@ -21027,7 +21027,7 @@
           <t>H | 379呎 (1房)
 $724万
 $19,100/呎
-(25年-06月-29日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J19" s="23" t="inlineStr">
@@ -21035,7 +21035,7 @@
           <t>J | 414呎 (1房)
 $770万
 $18,607/呎
-(25年-06月-12日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -21050,7 +21050,7 @@
           <t>A | 888呎 (3房)
 $3010万
 $33,900/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -21058,7 +21058,7 @@
           <t>B | 550呎 (2房)
 $1804万
 $32,800/呎
-(25年-12月-29日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -21066,7 +21066,7 @@
           <t>C | 543呎 (2房)
 $1801万
 $33,166/呎
-(25年-12月-29日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -21074,7 +21074,7 @@
           <t>D | 479呎 (2房)
 $1515万
 $31,626/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
@@ -21082,7 +21082,7 @@
           <t>E | 573呎 (2房)
 $1497万
 $26,125/呎
-(22年-08月-04日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
@@ -21090,7 +21090,7 @@
           <t>F | 381呎 (1房)
 $715万
 $18,772/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
@@ -21098,7 +21098,7 @@
           <t>G | 380呎 (1房)
 $790万
 $20,797/呎
-(25年-08月-31日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
@@ -21106,7 +21106,7 @@
           <t>H | 379呎 (1房)
 $885万
 $23,346/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
@@ -21114,7 +21114,7 @@
           <t>J | 414呎 (1房)
 $768万
 $18,552/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -21129,7 +21129,7 @@
           <t>A | 888呎 (3房)
 $3038万
 $34,212/呎
-(22年-05月-17日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -21137,7 +21137,7 @@
           <t>B | 550呎 (2房)
 $1798万
 $32,691/呎
-(25年-12月-28日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -21145,7 +21145,7 @@
           <t>C | 543呎 (2房)
 $1796万
 $33,066/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -21153,7 +21153,7 @@
           <t>D | 479呎 (2房)
 $1465万
 $30,576/呎
-(23年-12月-28日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -21161,7 +21161,7 @@
           <t>E | 575呎 (2房)
 $1447万
 $25,163/呎
-(22年-07月-31日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -21169,7 +21169,7 @@
           <t>F | 381呎 (1房)
 $713万
 $18,717/呎
-(25年-06月-12日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
@@ -21177,7 +21177,7 @@
           <t>G | 380呎 (1房)
 $788万
 $20,740/呎
-(25年-09月-01日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -21185,7 +21185,7 @@
           <t>H | 379呎 (1房)
 $732万
 $19,312/呎
-(25年-06月-18日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J21" s="23" t="inlineStr">
@@ -21193,7 +21193,7 @@
           <t>J | 414呎 (1房)
 $779万
 $18,814/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -21208,7 +21208,7 @@
           <t>A | 888呎 (3房)
 $3110万
 $35,023/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -21216,7 +21216,7 @@
           <t>B | 550呎 (2房)
 $1886万
 $34,300/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -21232,7 +21232,7 @@
           <t>D | 479呎 (2房)
 $1447万
 $30,210/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
@@ -21240,7 +21240,7 @@
           <t>E | 575呎 (2房)
 $1443万
 $25,088/呎
-(22年-08月-07日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
@@ -21248,7 +21248,7 @@
           <t>F | 381呎 (1房)
 $711万
 $18,662/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
@@ -21256,7 +21256,7 @@
           <t>G | 380呎 (1房)
 $786万
 $20,675/呎
-(25年-08月-07日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -21264,7 +21264,7 @@
           <t>H | 379呎 (1房)
 $895万
 $23,604/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
@@ -21272,7 +21272,7 @@
           <t>J | 414呎 (1房)
 $763万
 $18,438/呎
-(25年-06月-10日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -21287,7 +21287,7 @@
           <t>A | 888呎 (3房)
 $2940万
 $33,108/呎
-(25年-08月-05日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -21295,7 +21295,7 @@
           <t>B | 550呎 (2房)
 $1741万
 $31,655/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -21303,7 +21303,7 @@
           <t>C | 543呎 (2房)
 $1742万
 $32,081/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -21311,7 +21311,7 @@
           <t>D | 479呎 (2房)
 $1443万
 $30,121/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
@@ -21319,7 +21319,7 @@
           <t>E | 575呎 (2房)
 $1453万
 $25,275/呎
-(22年-07月-26日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="G23" s="23" t="inlineStr">
@@ -21327,7 +21327,7 @@
           <t>F | 381呎 (1房)
 $933万
 $24,486/呎
-(23年-05月-02日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="H23" s="23" t="inlineStr">
@@ -21335,7 +21335,7 @@
           <t>G | 380呎 (1房)
 $932万
 $24,532/呎
-(23年-02月-01日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
@@ -21343,7 +21343,7 @@
           <t>H | 379呎 (1房)
 $951万
 $25,102/呎
-(22年-06月-16日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="J23" s="23" t="inlineStr">
@@ -21351,7 +21351,7 @@
           <t>J | 414呎 (1房)
 $842万
 $20,330/呎
-(25年-11月-18日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -21366,7 +21366,7 @@
           <t>A | 888呎 (3房)
 $2939万
 $33,100/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -21382,7 +21382,7 @@
           <t>C | 543呎 (2房)
 $1808万
 $33,297/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -21390,7 +21390,7 @@
           <t>D | 479呎 (2房)
 $1438万
 $30,011/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -21398,7 +21398,7 @@
           <t>E | 573呎 (2房)
 $1479万
 $25,819/呎
-(22年-08月-22日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
@@ -21406,7 +21406,7 @@
           <t>F | 381呎 (1房)
 $960万
 $25,184/呎
-(22年-07月-25日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
@@ -21414,7 +21414,7 @@
           <t>G | 380呎 (1房)
 $949万
 $24,975/呎
-(22年-08月-11日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -21422,7 +21422,7 @@
           <t>H | 379呎 (1房)
 $949万
 $25,028/呎
-(22年-05月-17日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
@@ -21430,7 +21430,7 @@
           <t>J | 414呎 (1房)
 $839万
 $20,266/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -21445,7 +21445,7 @@
           <t>A | 888呎 (3房)
 $2930万
 $33,000/呎
-(25年-10月-15日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -21469,7 +21469,7 @@
           <t>D | 476呎 (2房)
 $1461万
 $30,700/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -21477,7 +21477,7 @@
           <t>E | 573呎 (2房)
 $1328万
 $23,176/呎
-(25年-05月-01日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
@@ -21485,7 +21485,7 @@
           <t>F | 381呎 (1房)
 $715万
 $18,764/呎
-(25年-06月-23日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
@@ -21493,7 +21493,7 @@
           <t>G | 380呎 (1房)
 $969万
 $25,490/呎
-(22年-09月-05日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -21501,7 +21501,7 @@
           <t>H | 379呎 (1房)
 $939万
 $24,768/呎
-(22年-06月-08日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="J25" s="23" t="inlineStr">
@@ -21509,7 +21509,7 @@
           <t>J | 414呎 (1房)
 $839万
 $20,266/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -21524,7 +21524,7 @@
           <t>A | 888呎 (3房)
 $2930万
 $32,995/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -21556,7 +21556,7 @@
           <t>E | 573呎 (2房)
 $1505万
 $26,272/呎
-(22年-08月-24日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
@@ -21564,7 +21564,7 @@
           <t>F | 381呎 (1房)
 $705万
 $18,497/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H26" s="23" t="inlineStr">
@@ -21572,7 +21572,7 @@
           <t>G | 380呎 (1房)
 $936万
 $24,644/呎
-(23年-01月-25日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
@@ -21580,7 +21580,7 @@
           <t>H | 379呎 (1房)
 $936万
 $24,692/呎
-(22年-05月-17日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
@@ -21588,7 +21588,7 @@
           <t>J | 414呎 (1房)
 $836万
 $20,205/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -21603,7 +21603,7 @@
           <t>A | 888呎 (3房)
 $2920万
 $32,883/呎
-(25年-12月-28日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -21619,7 +21619,7 @@
           <t>C | 543呎 (2房)
 $1772万
 $32,640/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -21635,7 +21635,7 @@
           <t>E | 573呎 (2房)
 $1440万
 $25,136/呎
-(22年-08月-28日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
@@ -21643,7 +21643,7 @@
           <t>F | 381呎 (1房)
 $703万
 $18,441/呎
-(25年-06月-15日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H27" s="23" t="inlineStr">
@@ -21651,7 +21651,7 @@
           <t>G | 380呎 (1房)
 $924万
 $24,315/呎
-(23年-04月-19日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -21659,7 +21659,7 @@
           <t>H | 379呎 (1房)
 $933万
 $24,605/呎
-(22年-05月-18日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
@@ -21667,7 +21667,7 @@
           <t>J | 414呎 (1房)
 $914万
 $22,080/呎
-(25年-04月-21日)</t>
+(25年-04月)</t>
         </is>
       </c>
     </row>
@@ -21682,7 +21682,7 @@
           <t>A | 888呎 (3房)
 $2913万
 $32,800/呎
-(26年-01月-28日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -21690,7 +21690,7 @@
           <t>B | 550呎 (2房)
 $1766万
 $32,100/呎
-(26年-01月-28日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -21698,7 +21698,7 @@
           <t>C | 543呎 (2房)
 $1767万
 $32,540/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -21714,7 +21714,7 @@
           <t>E | 573呎 (2房)
 $1436万
 $25,060/呎
-(22年-09月-12日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -21722,7 +21722,7 @@
           <t>F | 381呎 (1房)
 $701万
 $18,386/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
@@ -21730,7 +21730,7 @@
           <t>G | 380呎 (1房)
 $700万
 $18,421/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
@@ -21738,7 +21738,7 @@
           <t>H | 379呎 (1房)
 $931万
 $24,560/呎
-(22年-05月-25日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
@@ -21746,7 +21746,7 @@
           <t>J | 414呎 (1房)
 $911万
 $22,012/呎
-(24年-05月-09日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21761,7 @@
           <t>A | 888呎 (3房)
 $2904万
 $32,700/呎
-(25年-08月-06日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -21777,7 +21777,7 @@
           <t>C | 543呎 (2房)
 $1789万
 $32,939/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -21793,7 +21793,7 @@
           <t>E | 573呎 (2房)
 $1497万
 $26,134/呎
-(22年-10月-26日)</t>
+(22年-10月)</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
@@ -21801,7 +21801,7 @@
           <t>F | 381呎 (1房)
 $739万
 $19,392/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
@@ -21809,7 +21809,7 @@
           <t>G | 380呎 (1房)
 $738万
 $19,429/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
@@ -21817,7 +21817,7 @@
           <t>H | 379呎 (1房)
 $745万
 $19,661/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
@@ -21825,7 +21825,7 @@
           <t>J | 414呎 (1房)
 $794万
 $19,167/呎
-(25年-06月-17日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -21840,7 +21840,7 @@
           <t>A | 888呎 (3房)
 $2859万
 $32,200/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -21872,7 +21872,7 @@
           <t>E | 575呎 (2房)
 $1423万
 $24,748/呎
-(22年-05月-16日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -21880,7 +21880,7 @@
           <t>F | 381呎 (1房)
 $914万
 $23,977/呎
-(22年-07月-28日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
@@ -21888,7 +21888,7 @@
           <t>G | 380呎 (1房)
 $694万
 $18,253/呎
-(25年-06月-12日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
@@ -21896,7 +21896,7 @@
           <t>H | 379呎 (1房)
 $922万
 $24,324/呎
-(22年-11月-06日)</t>
+(22年-11月)</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
@@ -21904,7 +21904,7 @@
           <t>J | 414呎 (1房)
 $745万
 $17,990/呎
-(25年-06月-15日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -21919,7 +21919,7 @@
           <t>A | 888呎 (3房)
 $2895万
 $32,600/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -21927,7 +21927,7 @@
           <t>B | 550呎 (2房)
 $1678万
 $30,509/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -21935,7 +21935,7 @@
           <t>C | 543呎 (2房)
 $1729万
 $31,841/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -21951,7 +21951,7 @@
           <t>E | 573呎 (2房)
 $1463万
 $25,531/呎
-(22年-09月-14日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
@@ -21959,7 +21959,7 @@
           <t>F | 381呎 (1房)
 $911万
 $23,904/呎
-(22年-10月-10日)</t>
+(22年-10月)</t>
         </is>
       </c>
       <c r="H31" s="23" t="inlineStr">
@@ -21967,7 +21967,7 @@
           <t>G | 380呎 (1房)
 $692万
 $18,200/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
@@ -21975,7 +21975,7 @@
           <t>H | 379呎 (1房)
 $919万
 $24,249/呎
-(23年-01月-31日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="J31" s="23" t="inlineStr">
@@ -21983,7 +21983,7 @@
           <t>J | 414呎 (1房)
 $900万
 $21,740/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -21998,7 +21998,7 @@
           <t>A | 888呎 (3房)
 $2895万
 $32,600/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -22006,7 +22006,7 @@
           <t>B | 550呎 (2房)
 $1754万
 $31,900/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -22014,7 +22014,7 @@
           <t>C | 543呎 (2房)
 $1756万
 $32,340/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -22030,7 +22030,7 @@
           <t>E | 573呎 (2房)
 $1463万
 $25,531/呎
-(22年-09月-21日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
@@ -22038,7 +22038,7 @@
           <t>F | 381呎 (1房)
 $692万
 $18,164/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H32" s="23" t="inlineStr">
@@ -22046,7 +22046,7 @@
           <t>G | 380呎 (1房)
 $692万
 $18,200/呎
-(25年-06月-25日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
@@ -22054,7 +22054,7 @@
           <t>H | 379呎 (1房)
 $698万
 $18,426/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J32" s="23" t="inlineStr">
@@ -22062,7 +22062,7 @@
           <t>J | 414呎 (1房)
 $743万
 $17,935/呎
-(25年-06月-11日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -22085,7 +22085,7 @@
           <t>B | 550呎 (2房)
 $1704万
 $30,982/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -22093,7 +22093,7 @@
           <t>C | 543呎 (2房)
 $1704万
 $31,381/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -22109,7 +22109,7 @@
           <t>E | 573呎 (2房)
 $1400万
 $24,433/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr">
@@ -22117,7 +22117,7 @@
           <t>F | 381呎 (1房)
 $690万
 $18,108/呎
-(25年-06月-18日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H33" s="23" t="inlineStr">
@@ -22125,7 +22125,7 @@
           <t>G | 380呎 (1房)
 $690万
 $18,145/呎
-(25年-06月-17日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I33" s="23" t="inlineStr">
@@ -22133,7 +22133,7 @@
           <t>H | 379呎 (1房)
 $696万
 $18,370/呎
-(25年-06月-17日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J33" s="23" t="inlineStr">
@@ -22141,7 +22141,7 @@
           <t>J | 414呎 (1房)
 $740万
 $17,880/呎
-(25年-06月-25日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -22156,7 +22156,7 @@
           <t>A | 888呎 (3房)
 $2877万
 $32,400/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -22188,7 +22188,7 @@
           <t>E | 573呎 (2房)
 $1445万
 $25,218/呎
-(22年-09月-28日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="G34" s="23" t="inlineStr">
@@ -22196,7 +22196,7 @@
           <t>F | 381呎 (1房)
 $704万
 $18,487/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H34" s="23" t="inlineStr">
@@ -22204,7 +22204,7 @@
           <t>G | 380呎 (1房)
 $732万
 $19,263/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I34" s="23" t="inlineStr">
@@ -22212,7 +22212,7 @@
           <t>H | 379呎 (1房)
 $841万
 $22,198/呎
-(24年-08月-29日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="J34" s="23" t="inlineStr">
@@ -22220,7 +22220,7 @@
           <t>J | 414呎 (1房)
 $895万
 $21,607/呎
-(24年-08月-29日)</t>
+(24年-08月)</t>
         </is>
       </c>
     </row>
@@ -22267,7 +22267,7 @@
           <t>E | 573呎 (2房)
 $1432万
 $24,985/呎
-(22年-10月-19日)</t>
+(22年-10月)</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr">
@@ -22275,7 +22275,7 @@
           <t>F | 381呎 (1房)
 $698万
 $18,318/呎
-(25年-06月-26日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H35" s="23" t="inlineStr">
@@ -22283,7 +22283,7 @@
           <t>G | 380呎 (1房)
 $697万
 $18,352/呎
-(25年-06月-24日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I35" s="23" t="inlineStr">
@@ -22291,7 +22291,7 @@
           <t>H | 379呎 (1房)
 $713万
 $18,811/呎
-(25年-06月-24日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J35" s="23" t="inlineStr">
@@ -22299,7 +22299,7 @@
           <t>J | 414呎 (1房)
 $813万
 $19,647/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -22346,7 +22346,7 @@
           <t>E | 573呎 (2房)
 $1369万
 $23,899/呎
-(23年-01月-08日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="G36" s="23" t="inlineStr">
@@ -22354,7 +22354,7 @@
           <t>F | 381呎 (1房)
 $696万
 $18,260/呎
-(25年-06月-26日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H36" s="23" t="inlineStr">
@@ -22362,7 +22362,7 @@
           <t>G | 380呎 (1房)
 $897万
 $23,613/呎
-(22年-05月-17日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="I36" s="23" t="inlineStr">
@@ -22370,7 +22370,7 @@
           <t>H | 379呎 (1房)
 $711万
 $18,754/呎
-(25年-06月-06日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J36" s="23" t="inlineStr">
@@ -22378,7 +22378,7 @@
           <t>J | 414呎 (1房)
 $811万
 $19,586/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -22425,7 +22425,7 @@
           <t>E | 573呎 (2房)
 $1390万
 $24,250/呎
-(22年-08月-16日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="G37" s="23" t="inlineStr">
@@ -22433,7 +22433,7 @@
           <t>F | 381呎 (1房)
 $691万
 $18,148/呎
-(25年-06月-26日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H37" s="23" t="inlineStr">
@@ -22441,7 +22441,7 @@
           <t>G | 380呎 (1房)
 $920万
 $24,200/呎
-(22年-08月-21日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="I37" s="23" t="inlineStr">
@@ -22449,7 +22449,7 @@
           <t>H | 379呎 (1房)
 $706万
 $18,638/呎
-(25年-06月-26日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J37" s="23" t="inlineStr">
@@ -22457,7 +22457,7 @@
           <t>J | 414呎 (1房)
 $806万
 $19,461/呎
-(25年-08月-21日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
           <t>E | 573呎 (2房)
 $1376万
 $24,020/呎
-(23年-02月-16日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="G38" s="23" t="inlineStr">
@@ -22491,7 +22491,7 @@
           <t>F | 381呎 (1房)
 $685万
 $17,969/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H38" s="23" t="inlineStr">
@@ -22499,7 +22499,7 @@
           <t>G | 380呎 (1房)
 $684万
 $18,002/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I38" s="23" t="inlineStr">
@@ -22507,7 +22507,7 @@
           <t>H | 379呎 (1房)
 $702万
 $18,523/呎
-(25年-07月-16日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="J38" s="23" t="inlineStr">
@@ -22515,7 +22515,7 @@
           <t>J | 414呎 (1房)
 $801万
 $19,336/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-The Henley II.xlsx
+++ b/files/九龙-启德-The Henley II.xlsx
@@ -19897,7 +19897,7 @@
           <t>E | 573呎 (2房)
 $2108万
 $36,789/呎
-(22年-11月)</t>
+(22年-11月-07日)</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
@@ -19905,7 +19905,7 @@
           <t>F | 381呎 (1房)
 $859万
 $22,546/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
@@ -19913,7 +19913,7 @@
           <t>G | 380呎 (1房)
 $858万
 $22,589/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -19944,7 +19944,7 @@
           <t>A | 888呎 (3房)
 $3163万
 $35,618/呎
-(25年-04月)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -19952,7 +19952,7 @@
           <t>B | 550呎 (2房)
 $1908万
 $34,700/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -19960,7 +19960,7 @@
           <t>C | 543呎 (2房)
 $1908万
 $35,135/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -19968,7 +19968,7 @@
           <t>D | 479呎 (2房)
 $1533万
 $31,998/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -19976,7 +19976,7 @@
           <t>E | 573呎 (2房)
 $1569万
 $27,381/呎
-(23年-06月)</t>
+(23年-06月-22日)</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
@@ -19984,7 +19984,7 @@
           <t>F | 381呎 (1房)
 $835万
 $21,919/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -19992,7 +19992,7 @@
           <t>G | 380呎 (1房)
 $835万
 $21,962/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
@@ -20000,7 +20000,7 @@
           <t>H | 379呎 (1房)
 $834万
 $22,009/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
@@ -20008,7 +20008,7 @@
           <t>J | 414呎 (1房)
 $919万
 $22,191/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
     </row>
@@ -20023,7 +20023,7 @@
           <t>A | 888呎 (3房)
 $3450万
 $38,851/呎
-(22年-05月)</t>
+(22年-05月-23日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -20031,7 +20031,7 @@
           <t>B | 550呎 (2房)
 $1886万
 $34,300/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -20039,7 +20039,7 @@
           <t>C | 543呎 (2房)
 $1886万
 $34,736/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -20047,7 +20047,7 @@
           <t>D | 479呎 (2房)
 $1523万
 $31,800/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -20055,7 +20055,7 @@
           <t>E | 575呎 (2房)
 $1548万
 $26,915/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -20063,7 +20063,7 @@
           <t>F | 381呎 (1房)
 $755万
 $19,806/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
@@ -20071,7 +20071,7 @@
           <t>G | 380呎 (1房)
 $825万
 $21,718/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
@@ -20079,7 +20079,7 @@
           <t>H | 379呎 (1房)
 $825万
 $21,762/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
@@ -20087,7 +20087,7 @@
           <t>J | 414呎 (1房)
 $898万
 $21,691/呎
-(25年-08月)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -20102,7 +20102,7 @@
           <t>A | 888呎 (3房)
 $3313万
 $37,309/呎
-(23年-11月)</t>
+(23年-11月-30日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -20110,7 +20110,7 @@
           <t>B | 550呎 (2房)
 $1876万
 $34,100/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -20118,7 +20118,7 @@
           <t>C | 543呎 (2房)
 $1873万
 $34,490/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -20126,7 +20126,7 @@
           <t>D | 479呎 (2房)
 $1553万
 $32,412/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -20134,7 +20134,7 @@
           <t>E | 575呎 (2房)
 $1523万
 $26,483/呎
-(22年-07月)</t>
+(22年-07月-21日)</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -20142,7 +20142,7 @@
           <t>F | 381呎 (1房)
 $750万
 $19,696/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -20150,7 +20150,7 @@
           <t>G | 380呎 (1房)
 $821万
 $21,596/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
@@ -20158,7 +20158,7 @@
           <t>H | 379呎 (1房)
 $820万
 $21,639/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
@@ -20166,7 +20166,7 @@
           <t>J | 414呎 (1房)
 $903万
 $21,808/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
     </row>
@@ -20181,7 +20181,7 @@
           <t>A | 888呎 (3房)
 $3081万
 $34,700/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -20189,7 +20189,7 @@
           <t>B | 550呎 (2房)
 $1870万
 $34,000/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -20197,7 +20197,7 @@
           <t>C | 543呎 (2房)
 $1866万
 $34,359/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -20205,7 +20205,7 @@
           <t>D | 479呎 (2房)
 $1506万
 $31,435/呎
-(25年-02月)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -20213,7 +20213,7 @@
           <t>E | 573呎 (2房)
 $1518万
 $26,499/呎
-(22年-07月)</t>
+(22年-07月-24日)</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
@@ -20221,7 +20221,7 @@
           <t>F | 381呎 (1房)
 $748万
 $19,638/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
@@ -20229,7 +20229,7 @@
           <t>G | 380呎 (1房)
 $818万
 $21,534/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -20237,7 +20237,7 @@
           <t>H | 379呎 (1房)
 $818万
 $21,579/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr">
@@ -20245,7 +20245,7 @@
           <t>J | 414呎 (1房)
 $880万
 $21,260/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -20260,7 +20260,7 @@
           <t>A | 888呎 (3房)
 $3072万
 $34,600/呎
-(25年-03月)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -20268,7 +20268,7 @@
           <t>B | 550呎 (2房)
 $1864万
 $33,900/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -20276,7 +20276,7 @@
           <t>C | 543呎 (2房)
 $1958万
 $36,063/呎
-(22年-10月)</t>
+(22年-10月-26日)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -20284,7 +20284,7 @@
           <t>D | 479呎 (2房)
 $1580万
 $32,996/呎
-(22年-09月)</t>
+(22年-09月-04日)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -20292,7 +20292,7 @@
           <t>E | 573呎 (2房)
 $1546万
 $26,980/呎
-(22年-07月)</t>
+(22年-07月-27日)</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
@@ -20300,7 +20300,7 @@
           <t>F | 381呎 (1房)
 $746万
 $19,583/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -20308,7 +20308,7 @@
           <t>G | 380呎 (1房)
 $738万
 $19,418/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
@@ -20316,7 +20316,7 @@
           <t>H | 379呎 (1房)
 $745万
 $19,661/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
@@ -20324,7 +20324,7 @@
           <t>J | 414呎 (1房)
 $878万
 $21,196/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -20339,7 +20339,7 @@
           <t>A | 888呎 (3房)
 $3260万
 $36,712/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -20347,7 +20347,7 @@
           <t>B | 550呎 (2房)
 $1859万
 $33,800/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -20355,7 +20355,7 @@
           <t>C | 542呎 (2房)
 $1855万
 $34,225/呎
-(22年-12月)</t>
+(22年-12月-18日)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -20363,7 +20363,7 @@
           <t>D | 479呎 (2房)
 $1497万
 $31,255/呎
-(23年-01月)</t>
+(23年-01月-09日)</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
@@ -20371,7 +20371,7 @@
           <t>E | 573呎 (2房)
 $1557万
 $27,180/呎
-(22年-07月)</t>
+(22年-07月-31日)</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
@@ -20379,7 +20379,7 @@
           <t>F | 381呎 (1房)
 $744万
 $19,525/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
@@ -20387,7 +20387,7 @@
           <t>G | 380呎 (1房)
 $736万
 $19,361/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="I11" s="23" t="inlineStr">
@@ -20395,7 +20395,7 @@
           <t>H | 379呎 (1房)
 $743万
 $19,606/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
@@ -20403,7 +20403,7 @@
           <t>J | 414呎 (1房)
 $875万
 $21,135/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
     </row>
@@ -20418,7 +20418,7 @@
           <t>A | 888呎 (3房)
 $3215万
 $36,200/呎
-(24年-04月)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -20426,7 +20426,7 @@
           <t>B | 550呎 (2房)
 $1854万
 $33,700/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -20434,7 +20434,7 @@
           <t>C | 543呎 (2房)
 $1850万
 $34,062/呎
-(23年-04月)</t>
+(23年-04月-19日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -20442,7 +20442,7 @@
           <t>D | 479呎 (2房)
 $1493万
 $31,163/呎
-(23年-03月)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -20450,7 +20450,7 @@
           <t>E | 573呎 (2房)
 $1553万
 $27,101/呎
-(22年-08月)</t>
+(22年-08月-02日)</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
@@ -20458,7 +20458,7 @@
           <t>F | 381呎 (1房)
 $742万
 $19,473/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
@@ -20466,7 +20466,7 @@
           <t>G | 380呎 (1房)
 $734万
 $19,305/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
@@ -20474,7 +20474,7 @@
           <t>H | 379呎 (1房)
 $898万
 $23,697/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
@@ -20482,7 +20482,7 @@
           <t>J | 414呎 (1房)
 $872万
 $21,074/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -20497,7 +20497,7 @@
           <t>A | 888呎 (3房)
 $3189万
 $35,910/呎
-(23年-05月)</t>
+(23年-05月-15日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -20505,7 +20505,7 @@
           <t>B | 550呎 (2房)
 $1848万
 $33,600/呎
-(25年-02月)</t>
+(25年-02月-27日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -20513,7 +20513,7 @@
           <t>C | 543呎 (2房)
 $1844万
 $33,962/呎
-(23年-06月)</t>
+(23年-06月-28日)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -20521,7 +20521,7 @@
           <t>D | 479呎 (2房)
 $1488万
 $31,074/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -20529,7 +20529,7 @@
           <t>E | 573呎 (2房)
 $1383万
 $24,133/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
@@ -20537,7 +20537,7 @@
           <t>F | 381呎 (1房)
 $809万
 $21,246/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
@@ -20545,7 +20545,7 @@
           <t>G | 380呎 (1房)
 $732万
 $19,252/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -20553,7 +20553,7 @@
           <t>H | 379呎 (1房)
 $739万
 $19,492/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="J13" s="23" t="inlineStr">
@@ -20561,7 +20561,7 @@
           <t>J | 414呎 (1房)
 $870万
 $21,013/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
     </row>
@@ -20576,7 +20576,7 @@
           <t>A | 888呎 (3房)
 $3179万
 $35,800/呎
-(22年-06月)</t>
+(22年-06月-08日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -20584,7 +20584,7 @@
           <t>B | 550呎 (2房)
 $1842万
 $33,500/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -20592,7 +20592,7 @@
           <t>C | 543呎 (2房)
 $1839万
 $33,862/呎
-(23年-08月)</t>
+(23年-08月-28日)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -20600,7 +20600,7 @@
           <t>D | 479呎 (2房)
 $1547万
 $32,287/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
@@ -20608,7 +20608,7 @@
           <t>E | 575呎 (2房)
 $1497万
 $26,030/呎
-(22年-08月)</t>
+(22年-08月-10日)</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
@@ -20616,7 +20616,7 @@
           <t>F | 381呎 (1房)
 $807万
 $21,186/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
@@ -20624,7 +20624,7 @@
           <t>G | 380呎 (1房)
 $884万
 $23,268/呎
-(24年-12月)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
@@ -20632,7 +20632,7 @@
           <t>H | 379呎 (1房)
 $893万
 $23,560/呎
-(24年-12月)</t>
+(24年-12月-01日)</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
@@ -20640,7 +20640,7 @@
           <t>J | 414呎 (1房)
 $867万
 $20,949/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -20655,7 +20655,7 @@
           <t>A | 888呎 (3房)
 $3030万
 $34,122/呎
-(24年-12月)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -20663,7 +20663,7 @@
           <t>B | 550呎 (2房)
 $1837万
 $33,400/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -20671,7 +20671,7 @@
           <t>C | 543呎 (2房)
 $1833万
 $33,763/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -20679,7 +20679,7 @@
           <t>D | 479呎 (2房)
 $1480万
 $30,892/呎
-(25年-01月)</t>
+(25年-01月-19日)</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
@@ -20687,7 +20687,7 @@
           <t>E | 573呎 (2房)
 $1492万
 $26,045/呎
-(22年-08月)</t>
+(22年-08月-08日)</t>
         </is>
       </c>
       <c r="G15" s="23" t="inlineStr">
@@ -20695,7 +20695,7 @@
           <t>F | 381呎 (1房)
 $805万
 $21,126/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="H15" s="23" t="inlineStr">
@@ -20703,7 +20703,7 @@
           <t>G | 380呎 (1房)
 $727万
 $19,142/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="I15" s="23" t="inlineStr">
@@ -20711,7 +20711,7 @@
           <t>H | 379呎 (1房)
 $967万
 $25,504/呎
-(23年-04月)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="J15" s="23" t="inlineStr">
@@ -20719,7 +20719,7 @@
           <t>J | 414呎 (1房)
 $865万
 $20,886/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -20734,7 +20734,7 @@
           <t>A | 888呎 (3房)
 $3010万
 $33,896/呎
-(23年-10月)</t>
+(23年-10月-19日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -20742,7 +20742,7 @@
           <t>B | 550呎 (2房)
 $1832万
 $33,300/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -20750,7 +20750,7 @@
           <t>C | 543呎 (2房)
 $1905万
 $35,080/呎
-(22年-09月)</t>
+(22年-09月-15日)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -20758,7 +20758,7 @@
           <t>D | 476呎 (2房)
 $1475万
 $30,995/呎
-(23年-02月)</t>
+(23年-02月-20日)</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -20766,7 +20766,7 @@
           <t>E | 573呎 (2房)
 $1519万
 $26,515/呎
-(22年-08月)</t>
+(22年-08月-14日)</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
@@ -20774,7 +20774,7 @@
           <t>F | 381呎 (1房)
 $726万
 $19,050/呎
-(25年-06月)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
@@ -20782,7 +20782,7 @@
           <t>G | 380呎 (1房)
 $889万
 $23,399/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
@@ -20790,7 +20790,7 @@
           <t>H | 379呎 (1房)
 $964万
 $25,432/呎
-(22年-05月)</t>
+(22年-05月-16日)</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
@@ -20798,7 +20798,7 @@
           <t>J | 414呎 (1房)
 $862万
 $20,827/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -20813,7 +20813,7 @@
           <t>A | 888呎 (3房)
 $2948万
 $33,200/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -20821,7 +20821,7 @@
           <t>B | 550呎 (2房)
 $1820万
 $33,100/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -20829,7 +20829,7 @@
           <t>C | 543呎 (2房)
 $1817万
 $33,463/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -20837,7 +20837,7 @@
           <t>D | 479呎 (2房)
 $1467万
 $30,620/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -20845,7 +20845,7 @@
           <t>E | 573呎 (2房)
 $1557万
 $27,176/呎
-(22年-08月)</t>
+(22年-08月-14日)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -20853,7 +20853,7 @@
           <t>F | 381呎 (1房)
 $722万
 $18,938/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
@@ -20861,7 +20861,7 @@
           <t>G | 380呎 (1房)
 $797万
 $20,982/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="I17" s="23" t="inlineStr">
@@ -20869,7 +20869,7 @@
           <t>H | 379呎 (1房)
 $728万
 $19,213/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="J17" s="23" t="inlineStr">
@@ -20877,7 +20877,7 @@
           <t>J | 414呎 (1房)
 $775万
 $18,719/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -20892,7 +20892,7 @@
           <t>A | 888呎 (3房)
 $3019万
 $34,000/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -20900,7 +20900,7 @@
           <t>B | 550呎 (2房)
 $1815万
 $33,000/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -20908,7 +20908,7 @@
           <t>C | 543呎 (2房)
 $1812万
 $33,364/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -20916,7 +20916,7 @@
           <t>D | 479呎 (2房)
 $1462万
 $30,529/呎
-(23年-08月)</t>
+(23年-08月-13日)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -20924,7 +20924,7 @@
           <t>E | 573呎 (2房)
 $1553万
 $27,096/呎
-(22年-08月)</t>
+(22年-08月-07日)</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -20932,7 +20932,7 @@
           <t>F | 381呎 (1房)
 $719万
 $18,882/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
@@ -20940,7 +20940,7 @@
           <t>G | 380呎 (1房)
 $795万
 $20,922/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
@@ -20948,7 +20948,7 @@
           <t>H | 379呎 (1房)
 $880万
 $23,218/呎
-(25年-05月)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
@@ -20956,7 +20956,7 @@
           <t>J | 414呎 (1房)
 $773万
 $18,664/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -20971,7 +20971,7 @@
           <t>A | 888呎 (3房)
 $2984万
 $33,600/呎
-(25年-01月)</t>
+(25年-01月-05日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -20979,7 +20979,7 @@
           <t>B | 550呎 (2房)
 $1810万
 $32,900/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -20987,7 +20987,7 @@
           <t>C | 543呎 (2房)
 $1806万
 $33,266/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -20995,7 +20995,7 @@
           <t>D | 479呎 (2房)
 $1458万
 $30,440/呎
-(23年-02月)</t>
+(23年-02月-09日)</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -21003,7 +21003,7 @@
           <t>E | 575呎 (2房)
 $1471万
 $25,578/呎
-(22年-07月)</t>
+(22年-07月-31日)</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -21011,7 +21011,7 @@
           <t>F | 381呎 (1房)
 $717万
 $18,827/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
@@ -21019,7 +21019,7 @@
           <t>G | 380呎 (1房)
 $793万
 $20,859/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="I19" s="23" t="inlineStr">
@@ -21027,7 +21027,7 @@
           <t>H | 379呎 (1房)
 $724万
 $19,100/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="J19" s="23" t="inlineStr">
@@ -21035,7 +21035,7 @@
           <t>J | 414呎 (1房)
 $770万
 $18,607/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -21050,7 +21050,7 @@
           <t>A | 888呎 (3房)
 $3010万
 $33,900/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -21058,7 +21058,7 @@
           <t>B | 550呎 (2房)
 $1804万
 $32,800/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -21066,7 +21066,7 @@
           <t>C | 543呎 (2房)
 $1801万
 $33,166/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -21074,7 +21074,7 @@
           <t>D | 479呎 (2房)
 $1515万
 $31,626/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
@@ -21082,7 +21082,7 @@
           <t>E | 573呎 (2房)
 $1497万
 $26,125/呎
-(22年-08月)</t>
+(22年-08月-04日)</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
@@ -21090,7 +21090,7 @@
           <t>F | 381呎 (1房)
 $715万
 $18,772/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
@@ -21098,7 +21098,7 @@
           <t>G | 380呎 (1房)
 $790万
 $20,797/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
@@ -21106,7 +21106,7 @@
           <t>H | 379呎 (1房)
 $885万
 $23,346/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
@@ -21114,7 +21114,7 @@
           <t>J | 414呎 (1房)
 $768万
 $18,552/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -21129,7 +21129,7 @@
           <t>A | 888呎 (3房)
 $3038万
 $34,212/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -21137,7 +21137,7 @@
           <t>B | 550呎 (2房)
 $1798万
 $32,691/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -21145,7 +21145,7 @@
           <t>C | 543呎 (2房)
 $1796万
 $33,066/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -21153,7 +21153,7 @@
           <t>D | 479呎 (2房)
 $1465万
 $30,576/呎
-(23年-12月)</t>
+(23年-12月-28日)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -21161,7 +21161,7 @@
           <t>E | 575呎 (2房)
 $1447万
 $25,163/呎
-(22年-07月)</t>
+(22年-07月-31日)</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -21169,7 +21169,7 @@
           <t>F | 381呎 (1房)
 $713万
 $18,717/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
@@ -21177,7 +21177,7 @@
           <t>G | 380呎 (1房)
 $788万
 $20,740/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -21185,7 +21185,7 @@
           <t>H | 379呎 (1房)
 $732万
 $19,312/呎
-(25年-06月)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="J21" s="23" t="inlineStr">
@@ -21193,7 +21193,7 @@
           <t>J | 414呎 (1房)
 $779万
 $18,814/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
     </row>
@@ -21208,7 +21208,7 @@
           <t>A | 888呎 (3房)
 $3110万
 $35,023/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -21216,7 +21216,7 @@
           <t>B | 550呎 (2房)
 $1886万
 $34,300/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -21232,7 +21232,7 @@
           <t>D | 479呎 (2房)
 $1447万
 $30,210/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
@@ -21240,7 +21240,7 @@
           <t>E | 575呎 (2房)
 $1443万
 $25,088/呎
-(22年-08月)</t>
+(22年-08月-07日)</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
@@ -21248,7 +21248,7 @@
           <t>F | 381呎 (1房)
 $711万
 $18,662/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
@@ -21256,7 +21256,7 @@
           <t>G | 380呎 (1房)
 $786万
 $20,675/呎
-(25年-08月)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -21264,7 +21264,7 @@
           <t>H | 379呎 (1房)
 $895万
 $23,604/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
@@ -21272,7 +21272,7 @@
           <t>J | 414呎 (1房)
 $763万
 $18,438/呎
-(25年-06月)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -21287,7 +21287,7 @@
           <t>A | 888呎 (3房)
 $2940万
 $33,108/呎
-(25年-08月)</t>
+(25年-08月-05日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -21295,7 +21295,7 @@
           <t>B | 550呎 (2房)
 $1741万
 $31,655/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -21303,7 +21303,7 @@
           <t>C | 543呎 (2房)
 $1742万
 $32,081/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -21311,7 +21311,7 @@
           <t>D | 479呎 (2房)
 $1443万
 $30,121/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
@@ -21319,7 +21319,7 @@
           <t>E | 575呎 (2房)
 $1453万
 $25,275/呎
-(22年-07月)</t>
+(22年-07月-26日)</t>
         </is>
       </c>
       <c r="G23" s="23" t="inlineStr">
@@ -21327,7 +21327,7 @@
           <t>F | 381呎 (1房)
 $933万
 $24,486/呎
-(23年-05月)</t>
+(23年-05月-02日)</t>
         </is>
       </c>
       <c r="H23" s="23" t="inlineStr">
@@ -21335,7 +21335,7 @@
           <t>G | 380呎 (1房)
 $932万
 $24,532/呎
-(23年-02月)</t>
+(23年-02月-01日)</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
@@ -21343,7 +21343,7 @@
           <t>H | 379呎 (1房)
 $951万
 $25,102/呎
-(22年-06月)</t>
+(22年-06月-16日)</t>
         </is>
       </c>
       <c r="J23" s="23" t="inlineStr">
@@ -21351,7 +21351,7 @@
           <t>J | 414呎 (1房)
 $842万
 $20,330/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
     </row>
@@ -21366,7 +21366,7 @@
           <t>A | 888呎 (3房)
 $2939万
 $33,100/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -21382,7 +21382,7 @@
           <t>C | 543呎 (2房)
 $1808万
 $33,297/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -21390,7 +21390,7 @@
           <t>D | 479呎 (2房)
 $1438万
 $30,011/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -21398,7 +21398,7 @@
           <t>E | 573呎 (2房)
 $1479万
 $25,819/呎
-(22年-08月)</t>
+(22年-08月-22日)</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
@@ -21406,7 +21406,7 @@
           <t>F | 381呎 (1房)
 $960万
 $25,184/呎
-(22年-07月)</t>
+(22年-07月-25日)</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
@@ -21414,7 +21414,7 @@
           <t>G | 380呎 (1房)
 $949万
 $24,975/呎
-(22年-08月)</t>
+(22年-08月-11日)</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -21422,7 +21422,7 @@
           <t>H | 379呎 (1房)
 $949万
 $25,028/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
@@ -21430,7 +21430,7 @@
           <t>J | 414呎 (1房)
 $839万
 $20,266/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -21445,7 +21445,7 @@
           <t>A | 888呎 (3房)
 $2930万
 $33,000/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -21469,7 +21469,7 @@
           <t>D | 476呎 (2房)
 $1461万
 $30,700/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -21477,7 +21477,7 @@
           <t>E | 573呎 (2房)
 $1328万
 $23,176/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
@@ -21485,7 +21485,7 @@
           <t>F | 381呎 (1房)
 $715万
 $18,764/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
@@ -21493,7 +21493,7 @@
           <t>G | 380呎 (1房)
 $969万
 $25,490/呎
-(22年-09月)</t>
+(22年-09月-05日)</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -21501,7 +21501,7 @@
           <t>H | 379呎 (1房)
 $939万
 $24,768/呎
-(22年-06月)</t>
+(22年-06月-08日)</t>
         </is>
       </c>
       <c r="J25" s="23" t="inlineStr">
@@ -21509,7 +21509,7 @@
           <t>J | 414呎 (1房)
 $839万
 $20,266/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -21524,7 +21524,7 @@
           <t>A | 888呎 (3房)
 $2930万
 $32,995/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -21556,7 +21556,7 @@
           <t>E | 573呎 (2房)
 $1505万
 $26,272/呎
-(22年-08月)</t>
+(22年-08月-24日)</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
@@ -21564,7 +21564,7 @@
           <t>F | 381呎 (1房)
 $705万
 $18,497/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H26" s="23" t="inlineStr">
@@ -21572,7 +21572,7 @@
           <t>G | 380呎 (1房)
 $936万
 $24,644/呎
-(23年-01月)</t>
+(23年-01月-25日)</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
@@ -21580,7 +21580,7 @@
           <t>H | 379呎 (1房)
 $936万
 $24,692/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
@@ -21588,7 +21588,7 @@
           <t>J | 414呎 (1房)
 $836万
 $20,205/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -21603,7 +21603,7 @@
           <t>A | 888呎 (3房)
 $2920万
 $32,883/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -21619,7 +21619,7 @@
           <t>C | 543呎 (2房)
 $1772万
 $32,640/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -21635,7 +21635,7 @@
           <t>E | 573呎 (2房)
 $1440万
 $25,136/呎
-(22年-08月)</t>
+(22年-08月-28日)</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
@@ -21643,7 +21643,7 @@
           <t>F | 381呎 (1房)
 $703万
 $18,441/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="H27" s="23" t="inlineStr">
@@ -21651,7 +21651,7 @@
           <t>G | 380呎 (1房)
 $924万
 $24,315/呎
-(23年-04月)</t>
+(23年-04月-19日)</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -21659,7 +21659,7 @@
           <t>H | 379呎 (1房)
 $933万
 $24,605/呎
-(22年-05月)</t>
+(22年-05月-18日)</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
@@ -21667,7 +21667,7 @@
           <t>J | 414呎 (1房)
 $914万
 $22,080/呎
-(25年-04月)</t>
+(25年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -21682,7 +21682,7 @@
           <t>A | 888呎 (3房)
 $2913万
 $32,800/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -21690,7 +21690,7 @@
           <t>B | 550呎 (2房)
 $1766万
 $32,100/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -21698,7 +21698,7 @@
           <t>C | 543呎 (2房)
 $1767万
 $32,540/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -21714,7 +21714,7 @@
           <t>E | 573呎 (2房)
 $1436万
 $25,060/呎
-(22年-09月)</t>
+(22年-09月-12日)</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -21722,7 +21722,7 @@
           <t>F | 381呎 (1房)
 $701万
 $18,386/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
@@ -21730,7 +21730,7 @@
           <t>G | 380呎 (1房)
 $700万
 $18,421/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
@@ -21738,7 +21738,7 @@
           <t>H | 379呎 (1房)
 $931万
 $24,560/呎
-(22年-05月)</t>
+(22年-05月-25日)</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
@@ -21746,7 +21746,7 @@
           <t>J | 414呎 (1房)
 $911万
 $22,012/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21761,7 @@
           <t>A | 888呎 (3房)
 $2904万
 $32,700/呎
-(25年-08月)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -21777,7 +21777,7 @@
           <t>C | 543呎 (2房)
 $1789万
 $32,939/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -21793,7 +21793,7 @@
           <t>E | 573呎 (2房)
 $1497万
 $26,134/呎
-(22年-10月)</t>
+(22年-10月-26日)</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
@@ -21801,7 +21801,7 @@
           <t>F | 381呎 (1房)
 $739万
 $19,392/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
@@ -21809,7 +21809,7 @@
           <t>G | 380呎 (1房)
 $738万
 $19,429/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
@@ -21817,7 +21817,7 @@
           <t>H | 379呎 (1房)
 $745万
 $19,661/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
@@ -21825,7 +21825,7 @@
           <t>J | 414呎 (1房)
 $794万
 $19,167/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -21840,7 +21840,7 @@
           <t>A | 888呎 (3房)
 $2859万
 $32,200/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -21872,7 +21872,7 @@
           <t>E | 575呎 (2房)
 $1423万
 $24,748/呎
-(22年-05月)</t>
+(22年-05月-16日)</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -21880,7 +21880,7 @@
           <t>F | 381呎 (1房)
 $914万
 $23,977/呎
-(22年-07月)</t>
+(22年-07月-28日)</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
@@ -21888,7 +21888,7 @@
           <t>G | 380呎 (1房)
 $694万
 $18,253/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
@@ -21896,7 +21896,7 @@
           <t>H | 379呎 (1房)
 $922万
 $24,324/呎
-(22年-11月)</t>
+(22年-11月-06日)</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
@@ -21904,7 +21904,7 @@
           <t>J | 414呎 (1房)
 $745万
 $17,990/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -21919,7 +21919,7 @@
           <t>A | 888呎 (3房)
 $2895万
 $32,600/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -21927,7 +21927,7 @@
           <t>B | 550呎 (2房)
 $1678万
 $30,509/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -21935,7 +21935,7 @@
           <t>C | 543呎 (2房)
 $1729万
 $31,841/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -21951,7 +21951,7 @@
           <t>E | 573呎 (2房)
 $1463万
 $25,531/呎
-(22年-09月)</t>
+(22年-09月-14日)</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
@@ -21959,7 +21959,7 @@
           <t>F | 381呎 (1房)
 $911万
 $23,904/呎
-(22年-10月)</t>
+(22年-10月-10日)</t>
         </is>
       </c>
       <c r="H31" s="23" t="inlineStr">
@@ -21967,7 +21967,7 @@
           <t>G | 380呎 (1房)
 $692万
 $18,200/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
@@ -21975,7 +21975,7 @@
           <t>H | 379呎 (1房)
 $919万
 $24,249/呎
-(23年-01月)</t>
+(23年-01月-31日)</t>
         </is>
       </c>
       <c r="J31" s="23" t="inlineStr">
@@ -21983,7 +21983,7 @@
           <t>J | 414呎 (1房)
 $900万
 $21,740/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -21998,7 +21998,7 @@
           <t>A | 888呎 (3房)
 $2895万
 $32,600/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -22006,7 +22006,7 @@
           <t>B | 550呎 (2房)
 $1754万
 $31,900/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -22014,7 +22014,7 @@
           <t>C | 543呎 (2房)
 $1756万
 $32,340/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -22030,7 +22030,7 @@
           <t>E | 573呎 (2房)
 $1463万
 $25,531/呎
-(22年-09月)</t>
+(22年-09月-21日)</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
@@ -22038,7 +22038,7 @@
           <t>F | 381呎 (1房)
 $692万
 $18,164/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H32" s="23" t="inlineStr">
@@ -22046,7 +22046,7 @@
           <t>G | 380呎 (1房)
 $692万
 $18,200/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
@@ -22054,7 +22054,7 @@
           <t>H | 379呎 (1房)
 $698万
 $18,426/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="J32" s="23" t="inlineStr">
@@ -22062,7 +22062,7 @@
           <t>J | 414呎 (1房)
 $743万
 $17,935/呎
-(25年-06月)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -22085,7 +22085,7 @@
           <t>B | 550呎 (2房)
 $1704万
 $30,982/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -22093,7 +22093,7 @@
           <t>C | 543呎 (2房)
 $1704万
 $31,381/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -22109,7 +22109,7 @@
           <t>E | 573呎 (2房)
 $1400万
 $24,433/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr">
@@ -22117,7 +22117,7 @@
           <t>F | 381呎 (1房)
 $690万
 $18,108/呎
-(25年-06月)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="H33" s="23" t="inlineStr">
@@ -22125,7 +22125,7 @@
           <t>G | 380呎 (1房)
 $690万
 $18,145/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="I33" s="23" t="inlineStr">
@@ -22133,7 +22133,7 @@
           <t>H | 379呎 (1房)
 $696万
 $18,370/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="J33" s="23" t="inlineStr">
@@ -22141,7 +22141,7 @@
           <t>J | 414呎 (1房)
 $740万
 $17,880/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -22156,7 +22156,7 @@
           <t>A | 888呎 (3房)
 $2877万
 $32,400/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -22188,7 +22188,7 @@
           <t>E | 573呎 (2房)
 $1445万
 $25,218/呎
-(22年-09月)</t>
+(22年-09月-28日)</t>
         </is>
       </c>
       <c r="G34" s="23" t="inlineStr">
@@ -22196,7 +22196,7 @@
           <t>F | 381呎 (1房)
 $704万
 $18,487/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="H34" s="23" t="inlineStr">
@@ -22204,7 +22204,7 @@
           <t>G | 380呎 (1房)
 $732万
 $19,263/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="I34" s="23" t="inlineStr">
@@ -22212,7 +22212,7 @@
           <t>H | 379呎 (1房)
 $841万
 $22,198/呎
-(24年-08月)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
       <c r="J34" s="23" t="inlineStr">
@@ -22220,7 +22220,7 @@
           <t>J | 414呎 (1房)
 $895万
 $21,607/呎
-(24年-08月)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
     </row>
@@ -22267,7 +22267,7 @@
           <t>E | 573呎 (2房)
 $1432万
 $24,985/呎
-(22年-10月)</t>
+(22年-10月-19日)</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr">
@@ -22275,7 +22275,7 @@
           <t>F | 381呎 (1房)
 $698万
 $18,318/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="H35" s="23" t="inlineStr">
@@ -22283,7 +22283,7 @@
           <t>G | 380呎 (1房)
 $697万
 $18,352/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="I35" s="23" t="inlineStr">
@@ -22291,7 +22291,7 @@
           <t>H | 379呎 (1房)
 $713万
 $18,811/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="J35" s="23" t="inlineStr">
@@ -22299,7 +22299,7 @@
           <t>J | 414呎 (1房)
 $813万
 $19,647/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
     </row>
@@ -22346,7 +22346,7 @@
           <t>E | 573呎 (2房)
 $1369万
 $23,899/呎
-(23年-01月)</t>
+(23年-01月-08日)</t>
         </is>
       </c>
       <c r="G36" s="23" t="inlineStr">
@@ -22354,7 +22354,7 @@
           <t>F | 381呎 (1房)
 $696万
 $18,260/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="H36" s="23" t="inlineStr">
@@ -22362,7 +22362,7 @@
           <t>G | 380呎 (1房)
 $897万
 $23,613/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="I36" s="23" t="inlineStr">
@@ -22370,7 +22370,7 @@
           <t>H | 379呎 (1房)
 $711万
 $18,754/呎
-(25年-06月)</t>
+(25年-06月-06日)</t>
         </is>
       </c>
       <c r="J36" s="23" t="inlineStr">
@@ -22378,7 +22378,7 @@
           <t>J | 414呎 (1房)
 $811万
 $19,586/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -22425,7 +22425,7 @@
           <t>E | 573呎 (2房)
 $1390万
 $24,250/呎
-(22年-08月)</t>
+(22年-08月-16日)</t>
         </is>
       </c>
       <c r="G37" s="23" t="inlineStr">
@@ -22433,7 +22433,7 @@
           <t>F | 381呎 (1房)
 $691万
 $18,148/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="H37" s="23" t="inlineStr">
@@ -22441,7 +22441,7 @@
           <t>G | 380呎 (1房)
 $920万
 $24,200/呎
-(22年-08月)</t>
+(22年-08月-21日)</t>
         </is>
       </c>
       <c r="I37" s="23" t="inlineStr">
@@ -22449,7 +22449,7 @@
           <t>H | 379呎 (1房)
 $706万
 $18,638/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="J37" s="23" t="inlineStr">
@@ -22457,7 +22457,7 @@
           <t>J | 414呎 (1房)
 $806万
 $19,461/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
           <t>E | 573呎 (2房)
 $1376万
 $24,020/呎
-(23年-02月)</t>
+(23年-02月-16日)</t>
         </is>
       </c>
       <c r="G38" s="23" t="inlineStr">
@@ -22491,7 +22491,7 @@
           <t>F | 381呎 (1房)
 $685万
 $17,969/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="H38" s="23" t="inlineStr">
@@ -22499,7 +22499,7 @@
           <t>G | 380呎 (1房)
 $684万
 $18,002/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="I38" s="23" t="inlineStr">
@@ -22507,7 +22507,7 @@
           <t>H | 379呎 (1房)
 $702万
 $18,523/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="J38" s="23" t="inlineStr">
@@ -22515,7 +22515,7 @@
           <t>J | 414呎 (1房)
 $801万
 $19,336/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-The Henley II.xlsx
+++ b/files/九龙-启德-The Henley II.xlsx
@@ -15171,38 +15171,30 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H233" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I233" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H233" s="5" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="I233" s="5" t="n">
+        <v>32000</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K233" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L233" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K233" s="5" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>32000</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
@@ -15211,7 +15203,7 @@
       </c>
       <c r="N233" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -19792,7 +19784,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -19802,7 +19794,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -21843,12 +21835,12 @@
 (26年-02月-04日)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 550呎 (2房)
-招标单位
--
-(在售)</t>
+$1760万
+$32,000/呎
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
